--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.33-e07.1\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.39-fix-core-gpt\content\data\output\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E6F997-4079-414C-A678-CA78AF2C5ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C459EB13-74A2-4614-88B9-52ED36E04786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Infor" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="314">
   <si>
     <t xml:space="preserve">CORE (COst REport) - PC </t>
   </si>
@@ -1052,19 +1052,37 @@
     <t>Smart Airport en la nueva terminal de Puerto Vallarta</t>
   </si>
   <si>
+    <t>Software Development</t>
+  </si>
+  <si>
+    <t>CUST-GAP-TEST</t>
+  </si>
+  <si>
     <t>GAP</t>
   </si>
   <si>
     <t>SLFC 20250256445</t>
   </si>
   <si>
-    <t>LLUIS GUERRA GONZALEZ</t>
+    <t>SO-TEST-20250256445</t>
   </si>
   <si>
-    <t>Carlos Alvarez Gonzalez</t>
+    <t>E90001</t>
   </si>
   <si>
-    <t>Joan MARCER</t>
+    <t>PM Test</t>
+  </si>
+  <si>
+    <t>E90002</t>
+  </si>
+  <si>
+    <t>Practice Leader Test</t>
+  </si>
+  <si>
+    <t>E90003</t>
+  </si>
+  <si>
+    <t>Joan Marcer</t>
   </si>
   <si>
     <t>E91010</t>
@@ -1124,9 +1142,6 @@
     <t>Diseñador gráfico</t>
   </si>
   <si>
-    <t>Coste no disponible</t>
-  </si>
-  <si>
     <t>Agencia de Viajes</t>
   </si>
   <si>
@@ -1142,10 +1157,13 @@
     <t>Trabajos on site</t>
   </si>
   <si>
-    <t>PVR-OC-0005647</t>
+    <t>PO-TEST-001</t>
   </si>
   <si>
     <t>ARIBA-TEST-001</t>
+  </si>
+  <si>
+    <t>Generado por RPA: 2026-05-11 09:17:00 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Datos SAP/SF del ejemplo: valores de prueba hardcodeados para validacion. | Revisar: campos externos, intercompany y planificacion. | ADVERTENCIA: PPO contiene anualidades de horas fuera del periodo CORE planificado.</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1180,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.0"/>
     <numFmt numFmtId="171" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="55" x14ac:knownFonts="1">
+  <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1504,13 +1522,6 @@
       <color rgb="FFFF670A"/>
       <name val="Verdana"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -2006,7 +2017,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="322">
+  <cellXfs count="321">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2888,7 +2899,33 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -2920,18 +2957,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2946,21 +2971,6 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -7485,11 +7495,11 @@
       <c r="C2" s="62"/>
     </row>
     <row r="3" spans="2:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="291" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="291"/>
-      <c r="D3" s="291"/>
+      <c r="B3" s="298" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="298"/>
+      <c r="D3" s="298"/>
     </row>
     <row r="4" spans="2:16" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="63"/>
@@ -7617,13 +7627,13 @@
       <c r="B11" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="295" t="s">
+      <c r="C11" s="302" t="s">
         <v>275</v>
       </c>
-      <c r="D11" s="295"/>
-      <c r="E11" s="295"/>
-      <c r="F11" s="295"/>
-      <c r="G11" s="295"/>
+      <c r="D11" s="302"/>
+      <c r="E11" s="302"/>
+      <c r="F11" s="302"/>
+      <c r="G11" s="302"/>
       <c r="H11" s="29"/>
       <c r="I11" s="29"/>
       <c r="J11" s="29"/>
@@ -7638,10 +7648,10 @@
       <c r="B12" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="292" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="292"/>
+      <c r="C12" s="299" t="s">
+        <v>276</v>
+      </c>
+      <c r="D12" s="299"/>
       <c r="H12" s="29"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -7656,8 +7666,8 @@
       <c r="B13" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="293"/>
-      <c r="D13" s="294"/>
+      <c r="C13" s="300"/>
+      <c r="D13" s="301"/>
       <c r="H13" s="29"/>
       <c r="I13" s="29"/>
       <c r="J13" s="29"/>
@@ -7707,11 +7717,11 @@
       <c r="B16" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="15">
-        <v>461530</v>
+      <c r="C16" s="15" t="s">
+        <v>277</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
@@ -7748,7 +7758,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="29"/>
@@ -7768,8 +7778,8 @@
       <c r="B19" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="183">
-        <v>714603126</v>
+      <c r="C19" s="183" t="s">
+        <v>280</v>
       </c>
       <c r="D19" s="70"/>
       <c r="E19" s="75"/>
@@ -7827,11 +7837,11 @@
       <c r="B22" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="16">
-        <v>3900331</v>
+      <c r="C22" s="16" t="s">
+        <v>281</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E22" s="75"/>
       <c r="F22" s="187"/>
@@ -7850,11 +7860,11 @@
       <c r="B23" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="16">
-        <v>3659518</v>
+      <c r="C23" s="16" t="s">
+        <v>283</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E23" s="75"/>
       <c r="F23" s="187"/>
@@ -7873,11 +7883,11 @@
       <c r="B24" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="17">
-        <v>458354</v>
+      <c r="C24" s="17" t="s">
+        <v>285</v>
       </c>
       <c r="D24" s="184" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E24" s="75"/>
       <c r="F24" s="187"/>
@@ -8211,9 +8221,9 @@
       <c r="P40" s="29"/>
     </row>
     <row r="41" spans="2:16" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="288"/>
-      <c r="C41" s="289"/>
-      <c r="D41" s="290"/>
+      <c r="B41" s="295"/>
+      <c r="C41" s="296"/>
+      <c r="D41" s="297"/>
       <c r="E41" s="89"/>
       <c r="F41" s="29"/>
       <c r="G41" s="29"/>
@@ -8509,9 +8519,9 @@
       <c r="P56" s="29"/>
     </row>
     <row r="57" spans="2:16" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="288"/>
-      <c r="C57" s="289"/>
-      <c r="D57" s="290"/>
+      <c r="B57" s="295"/>
+      <c r="C57" s="296"/>
+      <c r="D57" s="297"/>
       <c r="E57" s="89"/>
       <c r="F57" s="29"/>
       <c r="G57" s="29"/>
@@ -8853,15 +8863,15 @@
       <c r="B4" s="82" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="292" t="s">
+      <c r="C4" s="299" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="292"/>
+      <c r="D4" s="299"/>
       <c r="E4" s="27"/>
-      <c r="F4" s="313" t="s">
+      <c r="F4" s="312" t="s">
         <v>232</v>
       </c>
-      <c r="G4" s="318"/>
+      <c r="G4" s="317"/>
       <c r="H4" s="242" t="s">
         <v>233</v>
       </c>
@@ -8871,26 +8881,26 @@
       <c r="J4" s="242" t="s">
         <v>235</v>
       </c>
-      <c r="K4" s="313" t="s">
+      <c r="K4" s="312" t="s">
         <v>236</v>
       </c>
-      <c r="L4" s="313"/>
-      <c r="M4" s="313"/>
-      <c r="N4" s="313"/>
+      <c r="L4" s="312"/>
+      <c r="M4" s="312"/>
+      <c r="N4" s="312"/>
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="82" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="312" t="s">
+      <c r="C5" s="311" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="312"/>
+      <c r="D5" s="311"/>
       <c r="E5" s="27"/>
-      <c r="F5" s="312" t="s">
+      <c r="F5" s="311" t="s">
         <v>239</v>
       </c>
-      <c r="G5" s="312"/>
+      <c r="G5" s="311"/>
       <c r="H5" s="244">
         <v>0.5</v>
       </c>
@@ -8900,24 +8910,24 @@
       <c r="J5" s="234" t="s">
         <v>238</v>
       </c>
-      <c r="K5" s="312"/>
-      <c r="L5" s="312"/>
-      <c r="M5" s="312"/>
-      <c r="N5" s="312"/>
+      <c r="K5" s="311"/>
+      <c r="L5" s="311"/>
+      <c r="M5" s="311"/>
+      <c r="N5" s="311"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="312" t="s">
+      <c r="C6" s="311" t="s">
         <v>241</v>
       </c>
-      <c r="D6" s="312"/>
+      <c r="D6" s="311"/>
       <c r="E6" s="27"/>
-      <c r="F6" s="312" t="s">
+      <c r="F6" s="311" t="s">
         <v>242</v>
       </c>
-      <c r="G6" s="312"/>
+      <c r="G6" s="311"/>
       <c r="H6" s="244">
         <v>0.1</v>
       </c>
@@ -8925,26 +8935,26 @@
         <v>1000</v>
       </c>
       <c r="J6" s="234"/>
-      <c r="K6" s="312"/>
-      <c r="L6" s="312"/>
-      <c r="M6" s="312"/>
-      <c r="N6" s="312"/>
+      <c r="K6" s="311"/>
+      <c r="L6" s="311"/>
+      <c r="M6" s="311"/>
+      <c r="N6" s="311"/>
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="317">
+      <c r="C7" s="316">
         <v>10000</v>
       </c>
-      <c r="D7" s="317"/>
+      <c r="D7" s="316"/>
       <c r="E7" s="243" t="s">
         <v>244</v>
       </c>
-      <c r="F7" s="312" t="s">
+      <c r="F7" s="311" t="s">
         <v>245</v>
       </c>
-      <c r="G7" s="312"/>
+      <c r="G7" s="311"/>
       <c r="H7" s="244">
         <v>0.2</v>
       </c>
@@ -8952,18 +8962,18 @@
         <v>2000</v>
       </c>
       <c r="J7" s="234"/>
-      <c r="K7" s="312"/>
-      <c r="L7" s="312"/>
-      <c r="M7" s="312"/>
-      <c r="N7" s="312"/>
+      <c r="K7" s="311"/>
+      <c r="L7" s="311"/>
+      <c r="M7" s="311"/>
+      <c r="N7" s="311"/>
     </row>
     <row r="8" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
-      <c r="F8" s="312" t="s">
+      <c r="F8" s="311" t="s">
         <v>246</v>
       </c>
-      <c r="G8" s="312"/>
+      <c r="G8" s="311"/>
       <c r="H8" s="244">
         <v>0.1</v>
       </c>
@@ -8971,18 +8981,18 @@
         <v>1000</v>
       </c>
       <c r="J8" s="234"/>
-      <c r="K8" s="312"/>
-      <c r="L8" s="312"/>
-      <c r="M8" s="312"/>
-      <c r="N8" s="312"/>
+      <c r="K8" s="311"/>
+      <c r="L8" s="311"/>
+      <c r="M8" s="311"/>
+      <c r="N8" s="311"/>
     </row>
     <row r="9" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="27"/>
       <c r="E9" s="61"/>
-      <c r="F9" s="312" t="s">
+      <c r="F9" s="311" t="s">
         <v>247</v>
       </c>
-      <c r="G9" s="312"/>
+      <c r="G9" s="311"/>
       <c r="H9" s="244">
         <v>0.1</v>
       </c>
@@ -8990,18 +9000,18 @@
         <v>1000</v>
       </c>
       <c r="J9" s="234"/>
-      <c r="K9" s="312"/>
-      <c r="L9" s="312"/>
-      <c r="M9" s="312"/>
-      <c r="N9" s="312"/>
+      <c r="K9" s="311"/>
+      <c r="L9" s="311"/>
+      <c r="M9" s="311"/>
+      <c r="N9" s="311"/>
       <c r="O9" s="29"/>
       <c r="P9" s="29"/>
     </row>
     <row r="10" spans="2:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="319" t="s">
+      <c r="C10" s="318" t="s">
         <v>211</v>
       </c>
-      <c r="D10" s="319"/>
+      <c r="D10" s="318"/>
       <c r="M10" s="29"/>
       <c r="N10" s="29"/>
       <c r="O10" s="29"/>
@@ -10079,12 +10089,12 @@
       <c r="W45" s="26"/>
     </row>
     <row r="46" spans="2:23" s="94" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="314" t="s">
+      <c r="B46" s="313" t="s">
         <v>227</v>
       </c>
-      <c r="C46" s="314"/>
-      <c r="D46" s="314"/>
-      <c r="E46" s="314"/>
+      <c r="C46" s="313"/>
+      <c r="D46" s="313"/>
+      <c r="E46" s="313"/>
       <c r="F46" s="225">
         <f>SUM(F13:F45)</f>
         <v>3000</v>
@@ -10248,16 +10258,16 @@
       <c r="R55" s="29"/>
     </row>
     <row r="56" spans="2:22" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="315" t="s">
+      <c r="B56" s="314" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="316"/>
-      <c r="D56" s="316"/>
-      <c r="E56" s="316"/>
-      <c r="F56" s="316"/>
-      <c r="G56" s="316"/>
-      <c r="H56" s="316"/>
-      <c r="I56" s="316"/>
+      <c r="C56" s="315"/>
+      <c r="D56" s="315"/>
+      <c r="E56" s="315"/>
+      <c r="F56" s="315"/>
+      <c r="G56" s="315"/>
+      <c r="H56" s="315"/>
+      <c r="I56" s="315"/>
       <c r="J56" s="179"/>
       <c r="K56" s="179"/>
       <c r="L56" s="179"/>
@@ -10374,16 +10384,16 @@
       <c r="M4" s="104"/>
     </row>
     <row r="5" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="320" t="s">
+      <c r="B5" s="319" t="s">
         <v>256</v>
       </c>
-      <c r="C5" s="320"/>
-      <c r="D5" s="321" t="s">
+      <c r="C5" s="319"/>
+      <c r="D5" s="320" t="s">
         <v>266</v>
       </c>
-      <c r="E5" s="321"/>
-      <c r="F5" s="321"/>
-      <c r="G5" s="321"/>
+      <c r="E5" s="320"/>
+      <c r="F5" s="320"/>
+      <c r="G5" s="320"/>
       <c r="H5" s="104"/>
       <c r="I5" s="104"/>
       <c r="J5" s="104"/>
@@ -10933,16 +10943,16 @@
       <c r="M14" s="104"/>
     </row>
     <row r="15" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="320" t="s">
+      <c r="B15" s="319" t="s">
         <v>261</v>
       </c>
-      <c r="C15" s="320"/>
-      <c r="D15" s="321" t="s">
+      <c r="C15" s="319"/>
+      <c r="D15" s="320" t="s">
         <v>257</v>
       </c>
-      <c r="E15" s="321"/>
-      <c r="F15" s="321"/>
-      <c r="G15" s="321"/>
+      <c r="E15" s="320"/>
+      <c r="F15" s="320"/>
+      <c r="G15" s="320"/>
       <c r="H15" s="104"/>
       <c r="I15" s="104"/>
       <c r="J15" s="104"/>
@@ -11449,16 +11459,16 @@
       <c r="M24" s="104"/>
     </row>
     <row r="25" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="320" t="s">
+      <c r="B25" s="319" t="s">
         <v>262</v>
       </c>
-      <c r="C25" s="320"/>
-      <c r="D25" s="321" t="s">
+      <c r="C25" s="319"/>
+      <c r="D25" s="320" t="s">
         <v>257</v>
       </c>
-      <c r="E25" s="321"/>
-      <c r="F25" s="321"/>
-      <c r="G25" s="321"/>
+      <c r="E25" s="320"/>
+      <c r="F25" s="320"/>
+      <c r="G25" s="320"/>
       <c r="H25" s="104"/>
       <c r="I25" s="104"/>
       <c r="J25" s="104"/>
@@ -11979,16 +11989,16 @@
       <c r="M34" s="104"/>
     </row>
     <row r="35" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="320" t="s">
+      <c r="B35" s="319" t="s">
         <v>263</v>
       </c>
-      <c r="C35" s="320"/>
-      <c r="D35" s="321" t="s">
+      <c r="C35" s="319"/>
+      <c r="D35" s="320" t="s">
         <v>257</v>
       </c>
-      <c r="E35" s="321"/>
-      <c r="F35" s="321"/>
-      <c r="G35" s="321"/>
+      <c r="E35" s="320"/>
+      <c r="F35" s="320"/>
+      <c r="G35" s="320"/>
       <c r="H35" s="104"/>
       <c r="I35" s="104"/>
       <c r="J35" s="104"/>
@@ -12493,16 +12503,16 @@
       <c r="M44" s="104"/>
     </row>
     <row r="45" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="320" t="s">
+      <c r="B45" s="319" t="s">
         <v>264</v>
       </c>
-      <c r="C45" s="320"/>
-      <c r="D45" s="321" t="s">
+      <c r="C45" s="319"/>
+      <c r="D45" s="320" t="s">
         <v>257</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-      <c r="G45" s="321"/>
+      <c r="E45" s="320"/>
+      <c r="F45" s="320"/>
+      <c r="G45" s="320"/>
       <c r="H45" s="104"/>
       <c r="I45" s="104"/>
       <c r="J45" s="104"/>
@@ -13007,16 +13017,16 @@
       <c r="M54" s="104"/>
     </row>
     <row r="55" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="320" t="s">
+      <c r="B55" s="319" t="s">
         <v>265</v>
       </c>
-      <c r="C55" s="320"/>
-      <c r="D55" s="321" t="s">
+      <c r="C55" s="319"/>
+      <c r="D55" s="320" t="s">
         <v>257</v>
       </c>
-      <c r="E55" s="321"/>
-      <c r="F55" s="321"/>
-      <c r="G55" s="321"/>
+      <c r="E55" s="320"/>
+      <c r="F55" s="320"/>
+      <c r="G55" s="320"/>
       <c r="H55" s="104"/>
       <c r="I55" s="104"/>
       <c r="J55" s="104"/>
@@ -13627,22 +13637,22 @@
       <c r="S4" s="29"/>
     </row>
     <row r="5" spans="2:27" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="300" t="s">
+      <c r="B5" s="304" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="300"/>
-      <c r="D5" s="300"/>
-      <c r="E5" s="300"/>
-      <c r="F5" s="300"/>
-      <c r="G5" s="300"/>
-      <c r="H5" s="300"/>
-      <c r="I5" s="300"/>
-      <c r="J5" s="300"/>
-      <c r="K5" s="300"/>
-      <c r="L5" s="300"/>
-      <c r="M5" s="300"/>
-      <c r="N5" s="300"/>
-      <c r="O5" s="300"/>
+      <c r="C5" s="304"/>
+      <c r="D5" s="304"/>
+      <c r="E5" s="304"/>
+      <c r="F5" s="304"/>
+      <c r="G5" s="304"/>
+      <c r="H5" s="304"/>
+      <c r="I5" s="304"/>
+      <c r="J5" s="304"/>
+      <c r="K5" s="304"/>
+      <c r="L5" s="304"/>
+      <c r="M5" s="304"/>
+      <c r="N5" s="304"/>
+      <c r="O5" s="304"/>
       <c r="P5" s="90"/>
       <c r="Q5" s="29"/>
       <c r="R5" s="90"/>
@@ -13711,12 +13721,12 @@
       <c r="U6" s="175"/>
     </row>
     <row r="7" spans="2:27" s="94" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="301" t="s">
+      <c r="B7" s="305" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="302"/>
-      <c r="D7" s="302"/>
-      <c r="E7" s="302"/>
+      <c r="C7" s="306"/>
+      <c r="D7" s="306"/>
+      <c r="E7" s="306"/>
       <c r="F7" s="33">
         <f t="shared" ref="F7" si="0">SUM(F12,F36)</f>
         <v>583896.55000000005</v>
@@ -13763,12 +13773,12 @@
       <c r="S7" s="27"/>
     </row>
     <row r="8" spans="2:27" s="94" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="303" t="s">
+      <c r="B8" s="307" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="303"/>
-      <c r="D8" s="303"/>
-      <c r="E8" s="303"/>
+      <c r="C8" s="307"/>
+      <c r="D8" s="307"/>
+      <c r="E8" s="307"/>
       <c r="F8" s="38">
         <f>F7</f>
         <v>583896.55000000005</v>
@@ -13838,22 +13848,22 @@
       <c r="S9" s="27"/>
     </row>
     <row r="10" spans="2:27" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="300" t="s">
+      <c r="B10" s="304" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="300"/>
-      <c r="D10" s="300"/>
-      <c r="E10" s="300"/>
-      <c r="F10" s="300"/>
-      <c r="G10" s="300"/>
-      <c r="H10" s="300"/>
-      <c r="I10" s="300"/>
-      <c r="J10" s="300"/>
-      <c r="K10" s="300"/>
-      <c r="L10" s="300"/>
-      <c r="M10" s="300"/>
-      <c r="N10" s="300"/>
-      <c r="O10" s="300"/>
+      <c r="C10" s="304"/>
+      <c r="D10" s="304"/>
+      <c r="E10" s="304"/>
+      <c r="F10" s="304"/>
+      <c r="G10" s="304"/>
+      <c r="H10" s="304"/>
+      <c r="I10" s="304"/>
+      <c r="J10" s="304"/>
+      <c r="K10" s="304"/>
+      <c r="L10" s="304"/>
+      <c r="M10" s="304"/>
+      <c r="N10" s="304"/>
+      <c r="O10" s="304"/>
       <c r="P10" s="90"/>
       <c r="Q10" s="29"/>
       <c r="R10" s="90"/>
@@ -14003,22 +14013,22 @@
       <c r="S13" s="29"/>
     </row>
     <row r="14" spans="2:27" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="300" t="s">
+      <c r="B14" s="304" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="300"/>
-      <c r="D14" s="300"/>
-      <c r="E14" s="300"/>
-      <c r="F14" s="300"/>
-      <c r="G14" s="300"/>
-      <c r="H14" s="300"/>
-      <c r="I14" s="300"/>
-      <c r="J14" s="300"/>
-      <c r="K14" s="300"/>
-      <c r="L14" s="300"/>
-      <c r="M14" s="300"/>
-      <c r="N14" s="300"/>
-      <c r="O14" s="300"/>
+      <c r="C14" s="304"/>
+      <c r="D14" s="304"/>
+      <c r="E14" s="304"/>
+      <c r="F14" s="304"/>
+      <c r="G14" s="304"/>
+      <c r="H14" s="304"/>
+      <c r="I14" s="304"/>
+      <c r="J14" s="304"/>
+      <c r="K14" s="304"/>
+      <c r="L14" s="304"/>
+      <c r="M14" s="304"/>
+      <c r="N14" s="304"/>
+      <c r="O14" s="304"/>
       <c r="P14" s="29"/>
       <c r="Q14" s="29"/>
       <c r="R14" s="29"/>
@@ -15267,12 +15277,12 @@
       </c>
     </row>
     <row r="36" spans="2:27" s="94" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="299" t="s">
+      <c r="B36" s="303" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="299"/>
-      <c r="D36" s="299"/>
-      <c r="E36" s="299"/>
+      <c r="C36" s="303"/>
+      <c r="D36" s="303"/>
+      <c r="E36" s="303"/>
       <c r="F36" s="55">
         <f>SUMIF(B16:B35,"AMPLIACION",F16:F35)</f>
         <v>0</v>
@@ -15327,12 +15337,12 @@
       <c r="AA36" s="176"/>
     </row>
     <row r="37" spans="2:27" s="94" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="299" t="s">
+      <c r="B37" s="303" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="299"/>
-      <c r="D37" s="299"/>
-      <c r="E37" s="299"/>
+      <c r="C37" s="303"/>
+      <c r="D37" s="303"/>
+      <c r="E37" s="303"/>
       <c r="F37" s="55">
         <f>SUMIF(B16:B35,"REESTIMACION",F16:F35)</f>
         <v>0</v>
@@ -15511,17 +15521,17 @@
       <c r="R48" s="29"/>
     </row>
     <row r="49" spans="2:18" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="296" t="s">
+      <c r="B49" s="287" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="297"/>
-      <c r="G49" s="297"/>
-      <c r="H49" s="297"/>
-      <c r="I49" s="297"/>
-      <c r="J49" s="298"/>
+      <c r="C49" s="288"/>
+      <c r="D49" s="288"/>
+      <c r="E49" s="288"/>
+      <c r="F49" s="288"/>
+      <c r="G49" s="288"/>
+      <c r="H49" s="288"/>
+      <c r="I49" s="288"/>
+      <c r="J49" s="289"/>
       <c r="K49" s="29"/>
       <c r="L49" s="29"/>
       <c r="M49" s="29"/>
@@ -15905,52 +15915,52 @@
     </row>
     <row r="7" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D7" t="s">
         <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>283</v>
-      </c>
-      <c r="F7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="G7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="H7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="I7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="J7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="K7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="L7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="M7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="N7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="O7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="P7" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q7" s="287" t="s">
-        <v>300</v>
+        <v>289</v>
+      </c>
+      <c r="F7">
+        <v>40</v>
+      </c>
+      <c r="G7">
+        <v>40</v>
+      </c>
+      <c r="H7">
+        <v>40</v>
+      </c>
+      <c r="I7">
+        <v>40</v>
+      </c>
+      <c r="J7">
+        <v>40</v>
+      </c>
+      <c r="K7">
+        <v>40</v>
+      </c>
+      <c r="L7">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>40</v>
+      </c>
+      <c r="N7">
+        <v>40</v>
+      </c>
+      <c r="O7">
+        <v>40</v>
+      </c>
+      <c r="P7">
+        <v>40</v>
+      </c>
+      <c r="Q7">
+        <v>40</v>
       </c>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
@@ -16015,52 +16025,52 @@
     </row>
     <row r="8" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D8" t="s">
         <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="G8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="H8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="I8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="J8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="K8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="L8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="M8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="N8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="O8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="P8" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q8" s="287" t="s">
-        <v>300</v>
+        <v>292</v>
+      </c>
+      <c r="F8">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>26</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>26</v>
+      </c>
+      <c r="L8">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>26</v>
+      </c>
+      <c r="N8">
+        <v>26</v>
+      </c>
+      <c r="O8">
+        <v>26</v>
+      </c>
+      <c r="P8">
+        <v>26</v>
+      </c>
+      <c r="Q8">
+        <v>26</v>
       </c>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
@@ -16125,52 +16135,52 @@
     </row>
     <row r="9" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D9" t="s">
         <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
-      </c>
-      <c r="F9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="G9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="H9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="I9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="J9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="K9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="L9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="M9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="N9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="O9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="P9" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q9" s="287" t="s">
-        <v>300</v>
+        <v>295</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>16</v>
+      </c>
+      <c r="H9">
+        <v>16</v>
+      </c>
+      <c r="I9">
+        <v>16</v>
+      </c>
+      <c r="J9">
+        <v>16</v>
+      </c>
+      <c r="K9">
+        <v>16</v>
+      </c>
+      <c r="L9">
+        <v>16</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+      <c r="N9">
+        <v>16</v>
+      </c>
+      <c r="O9">
+        <v>16</v>
+      </c>
+      <c r="P9">
+        <v>16</v>
+      </c>
+      <c r="Q9">
+        <v>16</v>
       </c>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
@@ -16235,10 +16245,10 @@
     </row>
     <row r="10" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C10" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D10" t="s">
         <v>91</v>
@@ -16246,41 +16256,41 @@
       <c r="E10" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="G10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="H10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="I10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="J10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="K10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="L10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="M10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="N10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="O10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="P10" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q10" s="287" t="s">
-        <v>300</v>
+      <c r="F10">
+        <v>38.75</v>
+      </c>
+      <c r="G10">
+        <v>38.75</v>
+      </c>
+      <c r="H10">
+        <v>38.75</v>
+      </c>
+      <c r="I10">
+        <v>38.75</v>
+      </c>
+      <c r="J10">
+        <v>38.75</v>
+      </c>
+      <c r="K10">
+        <v>38.75</v>
+      </c>
+      <c r="L10">
+        <v>38.75</v>
+      </c>
+      <c r="M10">
+        <v>38.75</v>
+      </c>
+      <c r="N10">
+        <v>38.75</v>
+      </c>
+      <c r="O10">
+        <v>38.75</v>
+      </c>
+      <c r="P10">
+        <v>38.75</v>
+      </c>
+      <c r="Q10">
+        <v>38.75</v>
       </c>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
@@ -16345,52 +16355,52 @@
     </row>
     <row r="11" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C11" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D11" t="s">
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>294</v>
-      </c>
-      <c r="F11" s="287" t="s">
         <v>300</v>
       </c>
-      <c r="G11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="H11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="I11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="J11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="K11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="L11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="M11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="N11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="O11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="P11" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q11" s="287" t="s">
-        <v>300</v>
+      <c r="F11">
+        <v>27</v>
+      </c>
+      <c r="G11">
+        <v>27</v>
+      </c>
+      <c r="H11">
+        <v>27</v>
+      </c>
+      <c r="I11">
+        <v>27</v>
+      </c>
+      <c r="J11">
+        <v>27</v>
+      </c>
+      <c r="K11">
+        <v>27</v>
+      </c>
+      <c r="L11">
+        <v>27</v>
+      </c>
+      <c r="M11">
+        <v>27</v>
+      </c>
+      <c r="N11">
+        <v>27</v>
+      </c>
+      <c r="O11">
+        <v>27</v>
+      </c>
+      <c r="P11">
+        <v>27</v>
+      </c>
+      <c r="Q11">
+        <v>27</v>
       </c>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
@@ -16455,52 +16465,52 @@
     </row>
     <row r="12" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C12" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>297</v>
-      </c>
-      <c r="F12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="G12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="H12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="I12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="J12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="K12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="L12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="M12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="N12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="O12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="P12" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q12" s="287" t="s">
-        <v>300</v>
+        <v>303</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>20</v>
+      </c>
+      <c r="I12">
+        <v>20</v>
+      </c>
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="K12">
+        <v>20</v>
+      </c>
+      <c r="L12">
+        <v>20</v>
+      </c>
+      <c r="M12">
+        <v>20</v>
+      </c>
+      <c r="N12">
+        <v>20</v>
+      </c>
+      <c r="O12">
+        <v>20</v>
+      </c>
+      <c r="P12">
+        <v>20</v>
+      </c>
+      <c r="Q12">
+        <v>20</v>
       </c>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
@@ -16553,7 +16563,7 @@
     </row>
     <row r="13" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C13" t="s">
         <v>123</v>
@@ -16562,43 +16572,43 @@
         <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>299</v>
-      </c>
-      <c r="F13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="G13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="H13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="I13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="J13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="K13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="L13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="M13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="N13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="O13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="P13" s="287" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q13" s="287" t="s">
-        <v>300</v>
+        <v>305</v>
+      </c>
+      <c r="F13">
+        <v>25</v>
+      </c>
+      <c r="G13">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>25</v>
+      </c>
+      <c r="J13">
+        <v>25</v>
+      </c>
+      <c r="K13">
+        <v>25</v>
+      </c>
+      <c r="L13">
+        <v>25</v>
+      </c>
+      <c r="M13">
+        <v>25</v>
+      </c>
+      <c r="N13">
+        <v>25</v>
+      </c>
+      <c r="O13">
+        <v>25</v>
+      </c>
+      <c r="P13">
+        <v>25</v>
+      </c>
+      <c r="Q13">
+        <v>25</v>
       </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
@@ -20113,7 +20123,7 @@
       <c r="H5" s="117"/>
       <c r="I5" s="118">
         <f>F5-SUM(F40:BN41)</f>
-        <v>367515.14</v>
+        <v>51845.140000000014</v>
       </c>
       <c r="J5" s="104"/>
       <c r="K5" s="280" t="s">
@@ -23627,51 +23637,51 @@
       </c>
       <c r="G40" s="124" cm="1">
         <f t="array" ref="G40">SUMPRODUCT(($D$10:$D$39="NO")*1,G$10:G$39,Resources!F7:F36)+G42</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H40" s="124" cm="1">
         <f t="array" ref="H40">SUMPRODUCT(($D$10:$D$39="NO")*1,H$10:H$39,Resources!G7:G36)+H42</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I40" s="124" cm="1">
         <f t="array" ref="I40">SUMPRODUCT(($D$10:$D$39="NO")*1,I$10:I$39,Resources!H7:H36)+I42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="J40" s="124" cm="1">
         <f t="array" ref="J40">SUMPRODUCT(($D$10:$D$39="NO")*1,J$10:J$39,Resources!I7:I36)+J42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="K40" s="124" cm="1">
         <f t="array" ref="K40">SUMPRODUCT(($D$10:$D$39="NO")*1,K$10:K$39,Resources!J7:J36)+K42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="L40" s="124" cm="1">
         <f t="array" ref="L40">SUMPRODUCT(($D$10:$D$39="NO")*1,L$10:L$39,Resources!K7:K36)+L42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="M40" s="124" cm="1">
         <f t="array" ref="M40">SUMPRODUCT(($D$10:$D$39="NO")*1,M$10:M$39,Resources!L7:L36)+M42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="N40" s="124" cm="1">
         <f t="array" ref="N40">SUMPRODUCT(($D$10:$D$39="NO")*1,N$10:N$39,Resources!M7:M36)+N42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="O40" s="124" cm="1">
         <f t="array" ref="O40">SUMPRODUCT(($D$10:$D$39="NO")*1,O$10:O$39,Resources!N7:N36)+O42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="P40" s="124" cm="1">
         <f t="array" ref="P40">SUMPRODUCT(($D$10:$D$39="NO")*1,P$10:P$39,Resources!O7:O36)+P42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="Q40" s="124" cm="1">
         <f t="array" ref="Q40">SUMPRODUCT(($D$10:$D$39="NO")*1,Q$10:Q$39,Resources!P7:P36)+Q42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="R40" s="124" cm="1">
         <f t="array" ref="R40">SUMPRODUCT(($D$10:$D$39="NO")*1,R$10:R$39,Resources!Q7:Q36)+R42</f>
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="S40" s="124" cm="1">
         <f t="array" ref="S40">SUMPRODUCT(($D$10:$D$39="NO")*1,S$10:S$39,Resources!R7:R36)+S42</f>
@@ -23876,51 +23886,51 @@
       <c r="F41" s="124"/>
       <c r="G41" s="124" cm="1">
         <f t="array" ref="G41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,G$10:G$39,Resources!F7:F36)+G43</f>
-        <v>0</v>
+        <v>17017.5</v>
       </c>
       <c r="H41" s="124" cm="1">
         <f t="array" ref="H41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,H$10:H$39,Resources!G7:G36)+H43</f>
-        <v>0</v>
+        <v>17017.5</v>
       </c>
       <c r="I41" s="124" cm="1">
         <f t="array" ref="I41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,I$10:I$39,Resources!H7:H36)+I43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="J41" s="124" cm="1">
         <f t="array" ref="J41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,J$10:J$39,Resources!I7:I36)+J43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="K41" s="124" cm="1">
         <f t="array" ref="K41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,K$10:K$39,Resources!J7:J36)+K43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="L41" s="124" cm="1">
         <f t="array" ref="L41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,L$10:L$39,Resources!K7:K36)+L43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="M41" s="124" cm="1">
         <f t="array" ref="M41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,M$10:M$39,Resources!L7:L36)+M43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="N41" s="124" cm="1">
         <f t="array" ref="N41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,N$10:N$39,Resources!M7:M36)+N43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="O41" s="124" cm="1">
         <f t="array" ref="O41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,O$10:O$39,Resources!N7:N36)+O43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="P41" s="124" cm="1">
         <f t="array" ref="P41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,P$10:P$39,Resources!O7:O36)+P43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="Q41" s="124" cm="1">
         <f t="array" ref="Q41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,Q$10:Q$39,Resources!P7:P36)+Q43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="R41" s="124" cm="1">
         <f t="array" ref="R41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,R$10:R$39,Resources!Q7:Q36)+R43</f>
-        <v>0</v>
+        <v>26243.5</v>
       </c>
       <c r="S41" s="124" cm="1">
         <f t="array" ref="S41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,S$10:S$39,Resources!R7:R36)+S43</f>
@@ -25120,10 +25130,10 @@
         <v>145</v>
       </c>
       <c r="C53" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D53" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E53" s="236"/>
       <c r="F53" s="236"/>
@@ -25225,10 +25235,10 @@
         <v>146</v>
       </c>
       <c r="C54" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D54" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E54" s="236"/>
       <c r="F54" s="236"/>
@@ -26229,16 +26239,16 @@
     </row>
     <row r="64" spans="2:79" s="109" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C64" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D64" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E64" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F64" s="11"/>
       <c r="G64">
@@ -31431,51 +31441,51 @@
       <c r="D18" s="156"/>
       <c r="E18" s="156">
         <f ca="1">E30-D30</f>
-        <v>26951.710732904849</v>
+        <v>50423.281817423354</v>
       </c>
       <c r="F18" s="156">
         <f ca="1">F30-E30</f>
-        <v>26951.710732904849</v>
+        <v>50423.281817423354</v>
       </c>
       <c r="G18" s="156">
         <f t="shared" ref="G18:AA18" ca="1" si="130">G30-F30</f>
-        <v>997.21329711747967</v>
+        <v>38842.13171549415</v>
       </c>
       <c r="H18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>997.21329711747967</v>
+        <v>38842.131715494121</v>
       </c>
       <c r="I18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>997.21329711747239</v>
+        <v>38842.13171549415</v>
       </c>
       <c r="J18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>997.21329711747967</v>
+        <v>38842.13171549415</v>
       </c>
       <c r="K18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>997.21329711747967</v>
+        <v>38842.131715494121</v>
       </c>
       <c r="L18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>997.21329711747967</v>
+        <v>38842.13171549415</v>
       </c>
       <c r="M18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>997.21329711747967</v>
+        <v>38842.13171549415</v>
       </c>
       <c r="N18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>997.21329711747967</v>
+        <v>38842.13171549415</v>
       </c>
       <c r="O18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>997.21329711747967</v>
+        <v>38842.131715494092</v>
       </c>
       <c r="P18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>521018.20886013302</v>
+        <v>133470.80092570611</v>
       </c>
       <c r="Q18" s="156">
         <f t="shared" ca="1" si="130"/>
@@ -31667,7 +31677,7 @@
       </c>
       <c r="BL18" s="156">
         <f t="shared" ref="BL18:BL24" ca="1" si="167">BL30-BK30</f>
-        <v>-495258.08716215141</v>
+        <v>-69865.760809347732</v>
       </c>
       <c r="BM18" s="26"/>
       <c r="BN18" s="26"/>
@@ -31950,51 +31960,51 @@
       <c r="D20" s="158"/>
       <c r="E20" s="158">
         <f t="shared" si="168"/>
-        <v>0</v>
+        <v>17417.5</v>
       </c>
       <c r="F20" s="158">
         <f t="shared" ref="F20:AA20" si="170">F32-E32</f>
-        <v>0</v>
+        <v>17417.5</v>
       </c>
       <c r="G20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="H20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="I20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="J20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="K20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="L20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="M20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="N20" s="158">
         <f>N32-M32</f>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="O20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="P20" s="158">
         <f t="shared" si="170"/>
-        <v>0</v>
+        <v>28083.5</v>
       </c>
       <c r="Q20" s="158">
         <f t="shared" si="170"/>
@@ -33221,51 +33231,51 @@
       <c r="D25" s="157"/>
       <c r="E25" s="157">
         <f>SUM(E20:E24)</f>
-        <v>20000</v>
+        <v>37417.5</v>
       </c>
       <c r="F25" s="157">
         <f t="shared" ref="F25:AA25" si="175">SUM(F20:F24)</f>
-        <v>20000</v>
+        <v>37417.5</v>
       </c>
       <c r="G25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="H25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="I25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="J25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="K25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="L25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="M25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="N25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="O25" s="157">
         <f t="shared" si="175"/>
-        <v>740</v>
+        <v>28823.5</v>
       </c>
       <c r="P25" s="157">
         <f t="shared" si="175"/>
-        <v>19115.759999999998</v>
+        <v>47199.259999999995</v>
       </c>
       <c r="Q25" s="157">
         <f t="shared" si="175"/>
@@ -33468,51 +33478,51 @@
       <c r="D26" s="159"/>
       <c r="E26" s="159">
         <f ca="1">E18-E25</f>
-        <v>6951.7107329048486</v>
+        <v>13005.781817423354</v>
       </c>
       <c r="F26" s="163">
         <f t="shared" ref="F26:Z26" ca="1" si="177">F18-F25</f>
-        <v>6951.7107329048486</v>
+        <v>13005.781817423354</v>
       </c>
       <c r="G26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747967</v>
+        <v>10018.63171549415</v>
       </c>
       <c r="H26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747967</v>
+        <v>10018.631715494121</v>
       </c>
       <c r="I26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747239</v>
+        <v>10018.63171549415</v>
       </c>
       <c r="J26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747967</v>
+        <v>10018.63171549415</v>
       </c>
       <c r="K26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747967</v>
+        <v>10018.631715494121</v>
       </c>
       <c r="L26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747967</v>
+        <v>10018.63171549415</v>
       </c>
       <c r="M26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747967</v>
+        <v>10018.63171549415</v>
       </c>
       <c r="N26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747967</v>
+        <v>10018.63171549415</v>
       </c>
       <c r="O26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>257.21329711747967</v>
+        <v>10018.631715494092</v>
       </c>
       <c r="P26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>501902.44886013301</v>
+        <v>86271.540925706111</v>
       </c>
       <c r="Q26" s="163">
         <f t="shared" ca="1" si="177"/>
@@ -33704,7 +33714,7 @@
       </c>
       <c r="BL26" s="159">
         <f t="shared" ca="1" si="178"/>
-        <v>-495258.08716215141</v>
+        <v>-69865.760809347732</v>
       </c>
     </row>
     <row r="27" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33715,51 +33725,51 @@
       <c r="D27" s="160"/>
       <c r="E27" s="160">
         <f ca="1">IF(E18=0,0,(E18-SUM(E20,E21,E22,E23,E24))/E18)</f>
-        <v>0.25793207718045269</v>
+        <v>0.25793207718045263</v>
       </c>
       <c r="F27" s="160">
         <f t="shared" ref="F27:Z27" ca="1" si="179">IF(F18=0,0,(F18-SUM(F20,F21,F22,F23,F24))/F18)</f>
-        <v>0.25793207718045269</v>
+        <v>0.25793207718045263</v>
       </c>
       <c r="G27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045291</v>
+        <v>0.2579320771804528</v>
       </c>
       <c r="H27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045291</v>
+        <v>0.25793207718045225</v>
       </c>
       <c r="I27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718044747</v>
+        <v>0.2579320771804528</v>
       </c>
       <c r="J27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045291</v>
+        <v>0.2579320771804528</v>
       </c>
       <c r="K27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045291</v>
+        <v>0.25793207718045225</v>
       </c>
       <c r="L27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045291</v>
+        <v>0.2579320771804528</v>
       </c>
       <c r="M27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045291</v>
+        <v>0.2579320771804528</v>
       </c>
       <c r="N27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045291</v>
+        <v>0.2579320771804528</v>
       </c>
       <c r="O27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045291</v>
+        <v>0.25793207718045169</v>
       </c>
       <c r="P27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.96331076404830296</v>
+        <v>0.6463701448358542</v>
       </c>
       <c r="Q27" s="160">
         <f t="shared" ca="1" si="179"/>
@@ -34233,47 +34243,47 @@
       </c>
       <c r="E30" s="156" cm="1">
         <f t="array" aca="1" ref="E30" ca="1">IF(E40,E40,E6*((E32+E33+E34+E35+E36)/(IF(E14&lt;margendirectofinal,E6-E14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>26951.710732904849</v>
+        <v>50423.281817423354</v>
       </c>
       <c r="F30" s="156" cm="1">
         <f t="array" aca="1" ref="F30" ca="1">IF(F40,F40,F6*((F32+F33+F34+F35+F36)/(IF(F14&lt;margendirectofinal,F6-F14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>53903.421465809697</v>
+        <v>100846.56363484671</v>
       </c>
       <c r="G30" s="156" cm="1">
         <f t="array" aca="1" ref="G30" ca="1">IF(G40,G40,G6*((G32+G33+G34+G35+G36)/(IF(G14&lt;margendirectofinal,G6-G14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>54900.634762927177</v>
+        <v>139688.69535034086</v>
       </c>
       <c r="H30" s="156" cm="1">
         <f t="array" aca="1" ref="H30" ca="1">IF(H40,H40,H6*((H32+H33+H34+H35+H36)/(IF(H14&lt;margendirectofinal,H6-H14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>55897.848060044656</v>
+        <v>178530.82706583498</v>
       </c>
       <c r="I30" s="156" cm="1">
         <f t="array" aca="1" ref="I30" ca="1">IF(I40,I40,I6*((I32+I33+I34+I35+I36)/(IF(I14&lt;margendirectofinal,I6-I14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>56895.061357162129</v>
+        <v>217372.95878132913</v>
       </c>
       <c r="J30" s="156" cm="1">
         <f t="array" aca="1" ref="J30" ca="1">IF(J40,J40,J6*((J32+J33+J34+J35+J36)/(IF(J14&lt;margendirectofinal,J6-J14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>57892.274654279609</v>
+        <v>256215.09049682328</v>
       </c>
       <c r="K30" s="156" cm="1">
         <f t="array" aca="1" ref="K30" ca="1">IF(K40,K40,K6*((K32+K33+K34+K35+K36)/(IF(K14&lt;margendirectofinal,K6-K14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>58889.487951397088</v>
+        <v>295057.2222123174</v>
       </c>
       <c r="L30" s="156" cm="1">
         <f t="array" aca="1" ref="L30" ca="1">IF(L40,L40,L6*((L32+L33+L34+L35+L36)/(IF(L14&lt;margendirectofinal,L6-L14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>59886.701248514568</v>
+        <v>333899.35392781155</v>
       </c>
       <c r="M30" s="156" cm="1">
         <f t="array" aca="1" ref="M30" ca="1">IF(M40,M40,M6*((M32+M33+M34+M35+M36)/(IF(M14&lt;margendirectofinal,M6-M14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>60883.914545632048</v>
+        <v>372741.4856433057</v>
       </c>
       <c r="N30" s="156" cm="1">
         <f t="array" aca="1" ref="N30" ca="1">IF(N40,N40,N6*((N32+N33+N34+N35+N36)/(IF(N14&lt;margendirectofinal,N6-N14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>61881.127842749527</v>
+        <v>411583.61735879985</v>
       </c>
       <c r="O30" s="156" cm="1">
         <f t="array" aca="1" ref="O30" ca="1">IF(O40,O40,O6*((O32+O33+O34+O35+O36)/(IF(O14&lt;margendirectofinal,O6-O14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>62878.341139867007</v>
+        <v>450425.74907429394</v>
       </c>
       <c r="P30" s="156" cm="1">
         <f t="array" aca="1" ref="P30" ca="1">IF(P40,P40,P6*((P32+P33+P34+P35+P36)/(IF(P14&lt;margendirectofinal,P6-P14,pedidobaselineactual-margendirectofinal))))</f>
@@ -34469,7 +34479,7 @@
       </c>
       <c r="BL30" s="156" cm="1">
         <f t="array" aca="1" ref="BL30" ca="1">IF(BL40,BL40,BL6*((BL32+BL33+BL34+BL35+BL36)/(IF(BL14&lt;margendirectofinal,BL6-BL14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>88638.462837848652</v>
+        <v>514030.78919065231</v>
       </c>
       <c r="BM30" s="26"/>
       <c r="BN30" s="26"/>
@@ -34758,243 +34768,243 @@
       </c>
       <c r="E32" s="164">
         <f>D32+LOOKUP(E$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(E$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>17417.5</v>
       </c>
       <c r="F32" s="164">
         <f>E32+LOOKUP(F$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(F$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>34835</v>
       </c>
       <c r="G32" s="164">
         <f>F32+LOOKUP(G$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(G$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>62918.5</v>
       </c>
       <c r="H32" s="164">
         <f>G32+LOOKUP(H$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(H$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>91002</v>
       </c>
       <c r="I32" s="164">
         <f>H32+LOOKUP(I$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(I$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>119085.5</v>
       </c>
       <c r="J32" s="164">
         <f>I32+LOOKUP(J$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(J$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>147169</v>
       </c>
       <c r="K32" s="164">
         <f>J32+LOOKUP(K$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(K$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>175252.5</v>
       </c>
       <c r="L32" s="164">
         <f>K32+LOOKUP(L$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(L$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>203336</v>
       </c>
       <c r="M32" s="164">
         <f>L32+LOOKUP(M$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(M$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>231419.5</v>
       </c>
       <c r="N32" s="164">
         <f>M32+LOOKUP(N$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(N$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>259503</v>
       </c>
       <c r="O32" s="164">
         <f>N32+LOOKUP(O$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(O$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>287586.5</v>
       </c>
       <c r="P32" s="164">
         <f>O32+LOOKUP(P$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(P$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="Q32" s="164">
         <f>P32+LOOKUP(Q$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(Q$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="R32" s="164">
         <f>Q32+LOOKUP(R$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(R$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="S32" s="164">
         <f>R32+LOOKUP(S$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(S$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="T32" s="164">
         <f>S32+LOOKUP(T$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(T$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="U32" s="164">
         <f>T32+LOOKUP(U$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(U$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="V32" s="164">
         <f>U32+LOOKUP(V$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(V$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="W32" s="164">
         <f>V32+LOOKUP(W$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(W$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="X32" s="164">
         <f>W32+LOOKUP(X$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(X$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="Y32" s="164">
         <f>X32+LOOKUP(Y$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(Y$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="Z32" s="164">
         <f>Y32+LOOKUP(Z$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(Z$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AA32" s="164">
         <f>Z32+LOOKUP(AA$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AA$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AB32" s="164">
         <f>AA32+LOOKUP(AB$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AB$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AC32" s="164">
         <f>AB32+LOOKUP(AC$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AC$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AD32" s="164">
         <f>AC32+LOOKUP(AD$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AD$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AE32" s="164">
         <f>AD32+LOOKUP(AE$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AE$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AF32" s="164">
         <f>AE32+LOOKUP(AF$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AF$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AG32" s="164">
         <f>AF32+LOOKUP(AG$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AG$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AH32" s="164">
         <f>AG32+LOOKUP(AH$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AH$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AI32" s="164">
         <f>AH32+LOOKUP(AI$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AI$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AJ32" s="164">
         <f>AI32+LOOKUP(AJ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AJ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AK32" s="164">
         <f>AJ32+LOOKUP(AK$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AK$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AL32" s="164">
         <f>AK32+LOOKUP(AL$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AL$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AM32" s="164">
         <f>AL32+LOOKUP(AM$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AM$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AN32" s="164">
         <f>AM32+LOOKUP(AN$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AN$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AO32" s="164">
         <f>AN32+LOOKUP(AO$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AO$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AP32" s="164">
         <f>AO32+LOOKUP(AP$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AP$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AQ32" s="164">
         <f>AP32+LOOKUP(AQ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AQ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AR32" s="164">
         <f>AQ32+LOOKUP(AR$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AR$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AS32" s="164">
         <f>AR32+LOOKUP(AS$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AS$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AT32" s="164">
         <f>AS32+LOOKUP(AT$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AT$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AU32" s="164">
         <f>AT32+LOOKUP(AU$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AU$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AV32" s="164">
         <f>AU32+LOOKUP(AV$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AV$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AW32" s="164">
         <f>AV32+LOOKUP(AW$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AW$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AX32" s="164">
         <f>AW32+LOOKUP(AX$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AX$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AY32" s="164">
         <f>AX32+LOOKUP(AY$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AY$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="AZ32" s="164">
         <f>AY32+LOOKUP(AZ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AZ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BA32" s="164">
         <f>AZ32+LOOKUP(BA$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BA$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BB32" s="164">
         <f>BA32+LOOKUP(BB$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BB$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BC32" s="164">
         <f>BB32+LOOKUP(BC$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BC$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BD32" s="164">
         <f>BC32+LOOKUP(BD$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BD$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BE32" s="164">
         <f>BD32+LOOKUP(BE$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BE$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BF32" s="164">
         <f>BE32+LOOKUP(BF$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BF$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BG32" s="164">
         <f>BF32+LOOKUP(BG$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BG$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BH32" s="164">
         <f>BG32+LOOKUP(BH$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BH$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BI32" s="164">
         <f>BH32+LOOKUP(BI$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BI$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BJ32" s="164">
         <f>BI32+LOOKUP(BJ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BJ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BK32" s="164">
         <f>BJ32+LOOKUP(BK$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BK$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BL32" s="164">
         <f>BK32+LOOKUP(BL$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BL$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="BN32" s="26"/>
       <c r="BO32" s="26"/>
@@ -36038,243 +36048,243 @@
       </c>
       <c r="E37" s="157">
         <f>SUM(E32:E36)</f>
-        <v>20000</v>
+        <v>37417.5</v>
       </c>
       <c r="F37" s="164">
         <f t="shared" ref="F37:AB37" si="240">SUM(F32:F36)</f>
-        <v>40000</v>
+        <v>74835</v>
       </c>
       <c r="G37" s="164">
         <f t="shared" si="240"/>
-        <v>40740</v>
+        <v>103658.5</v>
       </c>
       <c r="H37" s="164">
         <f t="shared" si="240"/>
-        <v>41480</v>
+        <v>132482</v>
       </c>
       <c r="I37" s="164">
         <f t="shared" si="240"/>
-        <v>42220</v>
+        <v>161305.5</v>
       </c>
       <c r="J37" s="164">
         <f t="shared" si="240"/>
-        <v>42960</v>
+        <v>190129</v>
       </c>
       <c r="K37" s="164">
         <f t="shared" si="240"/>
-        <v>43700</v>
+        <v>218952.5</v>
       </c>
       <c r="L37" s="164">
         <f t="shared" si="240"/>
-        <v>44440</v>
+        <v>247776</v>
       </c>
       <c r="M37" s="164">
         <f t="shared" si="240"/>
-        <v>45180</v>
+        <v>276599.5</v>
       </c>
       <c r="N37" s="164">
         <f t="shared" si="240"/>
-        <v>45920</v>
+        <v>305423</v>
       </c>
       <c r="O37" s="164">
         <f t="shared" si="240"/>
-        <v>46660</v>
+        <v>334246.5</v>
       </c>
       <c r="P37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="Q37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="R37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="S37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="T37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="U37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="V37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="W37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="X37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="Y37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="Z37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AA37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AB37" s="164">
         <f t="shared" si="240"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AC37" s="164">
         <f t="shared" ref="AC37:BL37" si="241">SUM(AC32:AC36)</f>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AD37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AE37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AF37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AG37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AH37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AI37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AJ37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AK37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AL37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AM37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AN37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AO37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AP37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AQ37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AR37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AS37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AT37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AU37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AV37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AW37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AX37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AY37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="AZ37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BA37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BB37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BC37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BD37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BE37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BF37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BG37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BH37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BI37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BJ37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BK37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="BL37" s="164">
         <f t="shared" si="241"/>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
     </row>
     <row r="38" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
@@ -36288,243 +36298,243 @@
       </c>
       <c r="E38" s="165">
         <f ca="1">E30-E32-E33-E34-E35-E36</f>
-        <v>6951.7107329048486</v>
+        <v>13005.781817423354</v>
       </c>
       <c r="F38" s="165">
         <f t="shared" ref="F38:Z38" ca="1" si="242">F30-F32-F33-F34-F35-F36</f>
-        <v>13903.421465809697</v>
+        <v>26011.563634846709</v>
       </c>
       <c r="G38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>14160.634762927177</v>
+        <v>36030.195350340859</v>
       </c>
       <c r="H38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>14417.848060044656</v>
+        <v>46048.827065834979</v>
       </c>
       <c r="I38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>14675.061357162129</v>
+        <v>56067.458781329129</v>
       </c>
       <c r="J38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>14932.274654279609</v>
+        <v>66086.090496823279</v>
       </c>
       <c r="K38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>15189.487951397088</v>
+        <v>76104.7222123174</v>
       </c>
       <c r="L38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>15446.701248514568</v>
+        <v>86123.35392781155</v>
       </c>
       <c r="M38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>15703.914545632048</v>
+        <v>96141.985643305699</v>
       </c>
       <c r="N38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>15961.127842749527</v>
+        <v>106160.61735879985</v>
       </c>
       <c r="O38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>16218.341139867007</v>
+        <v>116179.24907429394</v>
       </c>
       <c r="P38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="Q38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="R38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="S38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="T38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="U38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="V38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="W38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="X38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="Y38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="Z38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AA38" s="165">
         <f ca="1">AA30-AA32-AA33-AA34-AA35-AA36</f>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AB38" s="165">
         <f ca="1">AB30-AB32-AB33-AB34-AB35-AB36</f>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AC38" s="165">
         <f t="shared" ref="AC38:BL38" ca="1" si="243">AC30-AC32-AC33-AC34-AC35-AC36</f>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AD38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AE38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AF38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AG38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AH38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AI38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AJ38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AK38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AL38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AM38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AN38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AO38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AP38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AQ38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AR38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AS38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AT38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AU38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AV38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AW38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AX38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AY38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="AZ38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BA38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BB38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BC38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BD38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BE38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BF38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BG38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BH38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BI38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BJ38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BK38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="BL38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>22862.702837848658</v>
+        <v>132585.02919065231</v>
       </c>
     </row>
     <row r="39" spans="2:77" x14ac:dyDescent="0.3">
@@ -37251,47 +37261,47 @@
       <c r="D44" s="166"/>
       <c r="E44" s="166">
         <f t="shared" ref="E44:Z44" ca="1" si="284">E43-E30</f>
-        <v>-26951.710732904849</v>
+        <v>-50423.281817423354</v>
       </c>
       <c r="F44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-53903.421465809697</v>
+        <v>-100846.56363484671</v>
       </c>
       <c r="G44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-54900.634762927177</v>
+        <v>-139688.69535034086</v>
       </c>
       <c r="H44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-55897.848060044656</v>
+        <v>-178530.82706583498</v>
       </c>
       <c r="I44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-56895.061357162129</v>
+        <v>-217372.95878132913</v>
       </c>
       <c r="J44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-57892.274654279609</v>
+        <v>-256215.09049682328</v>
       </c>
       <c r="K44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-58889.487951397088</v>
+        <v>-295057.2222123174</v>
       </c>
       <c r="L44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-59886.701248514568</v>
+        <v>-333899.35392781155</v>
       </c>
       <c r="M44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-60883.914545632048</v>
+        <v>-372741.4856433057</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-61881.127842749527</v>
+        <v>-411583.61735879985</v>
       </c>
       <c r="O44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-62878.341139867007</v>
+        <v>-450425.74907429394</v>
       </c>
       <c r="P44" s="166">
         <f t="shared" ca="1" si="284"/>
@@ -37487,7 +37497,7 @@
       </c>
       <c r="BL44" s="166">
         <f t="shared" ca="1" si="285"/>
-        <v>-88638.462837848652</v>
+        <v>-514030.78919065231</v>
       </c>
       <c r="BN44" s="26"/>
       <c r="BO44" s="26"/>
@@ -38907,10 +38917,10 @@
       <c r="P5" s="93"/>
     </row>
     <row r="6" spans="2:16" s="94" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="305" t="s">
+      <c r="B6" s="291" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="306"/>
+      <c r="C6" s="292"/>
       <c r="D6" s="208">
         <f>'Cost Overview'!F12</f>
         <v>583896.55000000005</v>
@@ -38959,10 +38969,10 @@
       <c r="P6" s="27"/>
     </row>
     <row r="7" spans="2:16" s="94" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="307" t="s">
+      <c r="B7" s="293" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="307"/>
+      <c r="C7" s="293"/>
       <c r="D7" s="215">
         <f>'Cost Overview'!F8</f>
         <v>583896.55000000005</v>
@@ -39011,17 +39021,17 @@
       <c r="P7" s="27"/>
     </row>
     <row r="8" spans="2:16" s="94" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="307" t="s">
+      <c r="B8" s="293" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="307"/>
+      <c r="C8" s="293"/>
       <c r="D8" s="215">
         <f>D7</f>
         <v>583896.55000000005</v>
       </c>
       <c r="E8" s="215">
         <f>SUM('Cost Planning'!F40:BN41)</f>
-        <v>0</v>
+        <v>315670</v>
       </c>
       <c r="F8" s="215">
         <f>SUM('Cost Planning'!F9:BN9)</f>
@@ -39045,35 +39055,35 @@
       </c>
       <c r="K8" s="215">
         <f>SUM(E8,G8,H8,I8,J8)</f>
-        <v>65775.759999999995</v>
+        <v>381445.76</v>
       </c>
       <c r="L8" s="215">
         <f>D8-K8</f>
-        <v>518120.79000000004</v>
+        <v>202450.79000000004</v>
       </c>
       <c r="M8" s="216">
         <f>IF(D8=0,0,(D8-E8-H8-I8-G8-J8)/D8)</f>
-        <v>0.8873503191618447</v>
+        <v>0.34672373042793286</v>
       </c>
       <c r="N8" s="216">
         <f>IF(D8=0,0,(D8-E8/UTILIZACION-G8/UTILIZACION-H8/UTILIZACION-I8-J8)/D8)</f>
-        <v>0.88498154044508381</v>
+        <v>0.30366262782797443</v>
       </c>
       <c r="O8" s="29"/>
       <c r="P8" s="27"/>
     </row>
     <row r="9" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="308" t="s">
+      <c r="B9" s="294" t="s">
         <v>185</v>
       </c>
-      <c r="C9" s="308"/>
+      <c r="C9" s="294"/>
       <c r="D9" s="217">
         <f>IF(D8=0,1,(D8-D7)/D8)</f>
         <v>0</v>
       </c>
       <c r="E9" s="217">
         <f t="shared" ref="E9:L9" si="0">IF(E8=0,1,(E8-E7)/E8)</f>
-        <v>1</v>
+        <v>-0.16423841353312008</v>
       </c>
       <c r="F9" s="217">
         <f t="shared" si="0"/>
@@ -39097,15 +39107,15 @@
       </c>
       <c r="K9" s="217">
         <f t="shared" si="0"/>
-        <v>-5.5873948092732038</v>
+        <v>-0.13591746307522204</v>
       </c>
       <c r="L9" s="217">
         <f t="shared" si="0"/>
-        <v>0.70932328347604034</v>
+        <v>0.25608761516811074</v>
       </c>
       <c r="M9" s="218">
         <f>M8-M7</f>
-        <v>0.62941824198139207</v>
+        <v>8.8791653247480229E-2</v>
       </c>
       <c r="N9" s="239"/>
       <c r="O9" s="29"/>
@@ -39129,17 +39139,17 @@
       <c r="P10" s="29"/>
     </row>
     <row r="11" spans="2:16" s="94" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="306" t="s">
+      <c r="B11" s="292" t="s">
         <v>186</v>
       </c>
-      <c r="C11" s="306"/>
+      <c r="C11" s="292"/>
       <c r="D11" s="208">
         <f ca="1">SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$18:$BL$18)+'Project Infor'!C45</f>
-        <v>59886.701248514568</v>
+        <v>333899.35392781155</v>
       </c>
       <c r="E11" s="208">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$20:$BL$20)+'Project Infor'!C47</f>
-        <v>0</v>
+        <v>203336</v>
       </c>
       <c r="F11" s="208">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$19:$BL$19)+'Project Infor'!C46</f>
@@ -39163,35 +39173,35 @@
       </c>
       <c r="K11" s="208">
         <f>SUM(E11,G11,H11,I11,J11)</f>
-        <v>44440</v>
+        <v>247776</v>
       </c>
       <c r="L11" s="208">
         <f ca="1">D11-K11</f>
-        <v>15446.701248514568</v>
+        <v>86123.35392781155</v>
       </c>
       <c r="M11" s="209">
         <f ca="1">IF(D11=0,0,(D11-E11-H11-I11-G11-J11)/D11)</f>
-        <v>0.25793207718045263</v>
+        <v>0.25793207718045258</v>
       </c>
       <c r="N11" s="207">
         <f ca="1">IF(D11=0,0,(D11-E11/UTILIZACION-G11/UTILIZACION-H11/UTILIZACION-I11-J11)/D11)</f>
-        <v>0.25793207718045263</v>
+        <v>0.21209533016367751</v>
       </c>
       <c r="O11" s="29"/>
       <c r="P11" s="27"/>
     </row>
     <row r="12" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="304" t="s">
+      <c r="B12" s="290" t="s">
         <v>187</v>
       </c>
-      <c r="C12" s="304"/>
+      <c r="C12" s="290"/>
       <c r="D12" s="171">
         <f ca="1">IF(D11=0,1,(D11/D8))</f>
-        <v>0.10256388952548968</v>
+        <v>0.57184676622564656</v>
       </c>
       <c r="E12" s="171">
         <f>IF(E11=0,1,(E11/E8))</f>
-        <v>1</v>
+        <v>0.6441410333576203</v>
       </c>
       <c r="F12" s="171">
         <f>IF(F11=0,1,(F11/F8))</f>
@@ -39228,15 +39238,17 @@
       <c r="P17" s="29"/>
     </row>
     <row r="18" spans="2:16" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="296"/>
-      <c r="C18" s="297"/>
-      <c r="D18" s="297"/>
-      <c r="E18" s="297"/>
-      <c r="F18" s="297"/>
-      <c r="G18" s="297"/>
-      <c r="H18" s="297"/>
-      <c r="I18" s="297"/>
-      <c r="J18" s="298"/>
+      <c r="B18" s="287" t="s">
+        <v>313</v>
+      </c>
+      <c r="C18" s="288"/>
+      <c r="D18" s="288"/>
+      <c r="E18" s="288"/>
+      <c r="F18" s="288"/>
+      <c r="G18" s="288"/>
+      <c r="H18" s="288"/>
+      <c r="I18" s="288"/>
+      <c r="J18" s="289"/>
       <c r="K18" s="29"/>
       <c r="L18" s="29"/>
       <c r="M18" s="29"/>
@@ -39274,11 +39286,11 @@
   <sheetData>
     <row r="1" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="309" t="s">
+      <c r="B2" s="308" t="s">
         <v>189</v>
       </c>
-      <c r="C2" s="309"/>
-      <c r="D2" s="309"/>
+      <c r="C2" s="308"/>
+      <c r="D2" s="308"/>
     </row>
     <row r="3" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -39472,12 +39484,12 @@
         <f>'Cost Overview'!F8</f>
         <v>583896.55000000005</v>
       </c>
-      <c r="F5" s="311" t="s">
+      <c r="F5" s="310" t="s">
         <v>211</v>
       </c>
-      <c r="G5" s="311"/>
-      <c r="H5" s="311"/>
-      <c r="I5" s="311"/>
+      <c r="G5" s="310"/>
+      <c r="H5" s="310"/>
+      <c r="I5" s="310"/>
       <c r="J5" s="264">
         <f>E5-F41</f>
         <v>583896.55000000005</v>
@@ -40583,12 +40595,12 @@
       <c r="X40" s="254"/>
     </row>
     <row r="41" spans="2:24" s="268" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="310" t="s">
+      <c r="B41" s="309" t="s">
         <v>227</v>
       </c>
-      <c r="C41" s="310"/>
-      <c r="D41" s="310"/>
-      <c r="E41" s="310"/>
+      <c r="C41" s="309"/>
+      <c r="D41" s="309"/>
+      <c r="E41" s="309"/>
       <c r="F41" s="269">
         <f>SUM(F8:F40)</f>
         <v>0</v>
@@ -40760,17 +40772,17 @@
       <c r="S50" s="261"/>
     </row>
     <row r="51" spans="2:19" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="296" t="s">
+      <c r="B51" s="287" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="297"/>
-      <c r="D51" s="297"/>
-      <c r="E51" s="297"/>
-      <c r="F51" s="297"/>
-      <c r="G51" s="297"/>
-      <c r="H51" s="297"/>
-      <c r="I51" s="297"/>
-      <c r="J51" s="298"/>
+      <c r="C51" s="288"/>
+      <c r="D51" s="288"/>
+      <c r="E51" s="288"/>
+      <c r="F51" s="288"/>
+      <c r="G51" s="288"/>
+      <c r="H51" s="288"/>
+      <c r="I51" s="288"/>
+      <c r="J51" s="289"/>
       <c r="K51" s="273"/>
       <c r="L51" s="273"/>
       <c r="M51" s="273"/>
@@ -41445,17 +41457,17 @@
       <c r="AB19" s="29"/>
     </row>
     <row r="20" spans="2:28" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="296" t="s">
+      <c r="B20" s="287" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="297"/>
-      <c r="D20" s="297"/>
-      <c r="E20" s="297"/>
-      <c r="F20" s="297"/>
-      <c r="G20" s="297"/>
-      <c r="H20" s="297"/>
-      <c r="I20" s="297"/>
-      <c r="J20" s="298"/>
+      <c r="C20" s="288"/>
+      <c r="D20" s="288"/>
+      <c r="E20" s="288"/>
+      <c r="F20" s="288"/>
+      <c r="G20" s="288"/>
+      <c r="H20" s="288"/>
+      <c r="I20" s="288"/>
+      <c r="J20" s="289"/>
       <c r="K20" s="179"/>
       <c r="L20" s="179"/>
       <c r="M20" s="29"/>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.39-fix-core-gpt\content\data\output\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.36-e08\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C459EB13-74A2-4614-88B9-52ED36E04786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1F30C8-CE9B-4996-9BDF-2AA807FA729A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="308">
   <si>
     <t xml:space="preserve">CORE (COst REport) - PC </t>
   </si>
@@ -1052,37 +1052,19 @@
     <t>Smart Airport en la nueva terminal de Puerto Vallarta</t>
   </si>
   <si>
-    <t>Software Development</t>
-  </si>
-  <si>
-    <t>CUST-GAP-TEST</t>
-  </si>
-  <si>
     <t>GAP</t>
   </si>
   <si>
     <t>SLFC 20250256445</t>
   </si>
   <si>
-    <t>SO-TEST-20250256445</t>
+    <t>LLUIS GUERRA GONZALEZ</t>
   </si>
   <si>
-    <t>E90001</t>
+    <t>Carlos Alvarez Gonzalez</t>
   </si>
   <si>
-    <t>PM Test</t>
-  </si>
-  <si>
-    <t>E90002</t>
-  </si>
-  <si>
-    <t>Practice Leader Test</t>
-  </si>
-  <si>
-    <t>E90003</t>
-  </si>
-  <si>
-    <t>Joan Marcer</t>
+    <t>Joan MARCER</t>
   </si>
   <si>
     <t>E91010</t>
@@ -1157,13 +1139,13 @@
     <t>Trabajos on site</t>
   </si>
   <si>
-    <t>PO-TEST-001</t>
+    <t>PVR-OC-0005647</t>
   </si>
   <si>
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>Generado por RPA: 2026-05-11 09:17:00 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Datos SAP/SF del ejemplo: valores de prueba hardcodeados para validacion. | Revisar: campos externos, intercompany y planificacion. | ADVERTENCIA: PPO contiene anualidades de horas fuera del periodo CORE planificado.</t>
+    <t>Generado por RPA: 2026-05-11 10:17:02 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | ADVERTENCIA: PPO contiene anualidades de horas fuera del periodo CORE planificado.</t>
   </si>
 </sst>
 </file>
@@ -2983,13 +2965,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2999,9 +2974,16 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -7526,12 +7508,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="191">
-        <f>DATE(IF(EXACT(MONTH(EDATE(C5,0)),"12"),YEAR(C5)+1,YEAR(C5)),MONTH(EDATE(C5,1)),1)</f>
-        <v>46174</v>
+        <v>45961</v>
       </c>
       <c r="D6" s="68">
-        <f>DATE(YEAR(C6),MONTH(C6),1)</f>
-        <v>46174</v>
+        <v>45961</v>
       </c>
       <c r="E6" s="65"/>
       <c r="F6" s="72"/>
@@ -7649,7 +7629,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="299" t="s">
-        <v>276</v>
+        <v>47</v>
       </c>
       <c r="D12" s="299"/>
       <c r="H12" s="29"/>
@@ -7717,11 +7697,11 @@
       <c r="B16" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>277</v>
+      <c r="C16" s="15">
+        <v>461530</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
@@ -7758,7 +7738,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="29"/>
@@ -7778,8 +7758,8 @@
       <c r="B19" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="183" t="s">
-        <v>280</v>
+      <c r="C19" s="183">
+        <v>714603126</v>
       </c>
       <c r="D19" s="70"/>
       <c r="E19" s="75"/>
@@ -7837,11 +7817,11 @@
       <c r="B22" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>281</v>
+      <c r="C22" s="16">
+        <v>3900331</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E22" s="75"/>
       <c r="F22" s="187"/>
@@ -7860,11 +7840,11 @@
       <c r="B23" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>283</v>
+      <c r="C23" s="16">
+        <v>3659518</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E23" s="75"/>
       <c r="F23" s="187"/>
@@ -7883,11 +7863,11 @@
       <c r="B24" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>285</v>
+      <c r="C24" s="17">
+        <v>458354</v>
       </c>
       <c r="D24" s="184" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E24" s="75"/>
       <c r="F24" s="187"/>
@@ -8868,7 +8848,7 @@
       </c>
       <c r="D4" s="299"/>
       <c r="E4" s="27"/>
-      <c r="F4" s="312" t="s">
+      <c r="F4" s="316" t="s">
         <v>232</v>
       </c>
       <c r="G4" s="317"/>
@@ -8881,26 +8861,26 @@
       <c r="J4" s="242" t="s">
         <v>235</v>
       </c>
-      <c r="K4" s="312" t="s">
+      <c r="K4" s="316" t="s">
         <v>236</v>
       </c>
-      <c r="L4" s="312"/>
-      <c r="M4" s="312"/>
-      <c r="N4" s="312"/>
+      <c r="L4" s="316"/>
+      <c r="M4" s="316"/>
+      <c r="N4" s="316"/>
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="82" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="311" t="s">
+      <c r="C5" s="314" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="311"/>
+      <c r="D5" s="314"/>
       <c r="E5" s="27"/>
-      <c r="F5" s="311" t="s">
+      <c r="F5" s="314" t="s">
         <v>239</v>
       </c>
-      <c r="G5" s="311"/>
+      <c r="G5" s="314"/>
       <c r="H5" s="244">
         <v>0.5</v>
       </c>
@@ -8910,24 +8890,24 @@
       <c r="J5" s="234" t="s">
         <v>238</v>
       </c>
-      <c r="K5" s="311"/>
-      <c r="L5" s="311"/>
-      <c r="M5" s="311"/>
-      <c r="N5" s="311"/>
+      <c r="K5" s="314"/>
+      <c r="L5" s="314"/>
+      <c r="M5" s="314"/>
+      <c r="N5" s="314"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="311" t="s">
+      <c r="C6" s="314" t="s">
         <v>241</v>
       </c>
-      <c r="D6" s="311"/>
+      <c r="D6" s="314"/>
       <c r="E6" s="27"/>
-      <c r="F6" s="311" t="s">
+      <c r="F6" s="314" t="s">
         <v>242</v>
       </c>
-      <c r="G6" s="311"/>
+      <c r="G6" s="314"/>
       <c r="H6" s="244">
         <v>0.1</v>
       </c>
@@ -8935,26 +8915,26 @@
         <v>1000</v>
       </c>
       <c r="J6" s="234"/>
-      <c r="K6" s="311"/>
-      <c r="L6" s="311"/>
-      <c r="M6" s="311"/>
-      <c r="N6" s="311"/>
+      <c r="K6" s="314"/>
+      <c r="L6" s="314"/>
+      <c r="M6" s="314"/>
+      <c r="N6" s="314"/>
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="316">
+      <c r="C7" s="315">
         <v>10000</v>
       </c>
-      <c r="D7" s="316"/>
+      <c r="D7" s="315"/>
       <c r="E7" s="243" t="s">
         <v>244</v>
       </c>
-      <c r="F7" s="311" t="s">
+      <c r="F7" s="314" t="s">
         <v>245</v>
       </c>
-      <c r="G7" s="311"/>
+      <c r="G7" s="314"/>
       <c r="H7" s="244">
         <v>0.2</v>
       </c>
@@ -8962,18 +8942,18 @@
         <v>2000</v>
       </c>
       <c r="J7" s="234"/>
-      <c r="K7" s="311"/>
-      <c r="L7" s="311"/>
-      <c r="M7" s="311"/>
-      <c r="N7" s="311"/>
+      <c r="K7" s="314"/>
+      <c r="L7" s="314"/>
+      <c r="M7" s="314"/>
+      <c r="N7" s="314"/>
     </row>
     <row r="8" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
-      <c r="F8" s="311" t="s">
+      <c r="F8" s="314" t="s">
         <v>246</v>
       </c>
-      <c r="G8" s="311"/>
+      <c r="G8" s="314"/>
       <c r="H8" s="244">
         <v>0.1</v>
       </c>
@@ -8981,18 +8961,18 @@
         <v>1000</v>
       </c>
       <c r="J8" s="234"/>
-      <c r="K8" s="311"/>
-      <c r="L8" s="311"/>
-      <c r="M8" s="311"/>
-      <c r="N8" s="311"/>
+      <c r="K8" s="314"/>
+      <c r="L8" s="314"/>
+      <c r="M8" s="314"/>
+      <c r="N8" s="314"/>
     </row>
     <row r="9" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="27"/>
       <c r="E9" s="61"/>
-      <c r="F9" s="311" t="s">
+      <c r="F9" s="314" t="s">
         <v>247</v>
       </c>
-      <c r="G9" s="311"/>
+      <c r="G9" s="314"/>
       <c r="H9" s="244">
         <v>0.1</v>
       </c>
@@ -9000,10 +8980,10 @@
         <v>1000</v>
       </c>
       <c r="J9" s="234"/>
-      <c r="K9" s="311"/>
-      <c r="L9" s="311"/>
-      <c r="M9" s="311"/>
-      <c r="N9" s="311"/>
+      <c r="K9" s="314"/>
+      <c r="L9" s="314"/>
+      <c r="M9" s="314"/>
+      <c r="N9" s="314"/>
       <c r="O9" s="29"/>
       <c r="P9" s="29"/>
     </row>
@@ -10089,12 +10069,12 @@
       <c r="W45" s="26"/>
     </row>
     <row r="46" spans="2:23" s="94" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="313" t="s">
+      <c r="B46" s="311" t="s">
         <v>227</v>
       </c>
-      <c r="C46" s="313"/>
-      <c r="D46" s="313"/>
-      <c r="E46" s="313"/>
+      <c r="C46" s="311"/>
+      <c r="D46" s="311"/>
+      <c r="E46" s="311"/>
       <c r="F46" s="225">
         <f>SUM(F13:F45)</f>
         <v>3000</v>
@@ -10258,16 +10238,16 @@
       <c r="R55" s="29"/>
     </row>
     <row r="56" spans="2:22" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="314" t="s">
+      <c r="B56" s="312" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="315"/>
-      <c r="D56" s="315"/>
-      <c r="E56" s="315"/>
-      <c r="F56" s="315"/>
-      <c r="G56" s="315"/>
-      <c r="H56" s="315"/>
-      <c r="I56" s="315"/>
+      <c r="C56" s="313"/>
+      <c r="D56" s="313"/>
+      <c r="E56" s="313"/>
+      <c r="F56" s="313"/>
+      <c r="G56" s="313"/>
+      <c r="H56" s="313"/>
+      <c r="I56" s="313"/>
       <c r="J56" s="179"/>
       <c r="K56" s="179"/>
       <c r="L56" s="179"/>
@@ -10281,6 +10261,16 @@
   </sheetData>
   <autoFilter ref="B12:E12" xr:uid="{F0215733-3491-41E7-AEDA-44D9E214180D}"/>
   <mergeCells count="19">
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K8:N8"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="C4:D4"/>
@@ -10290,16 +10280,6 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C10">
@@ -15915,16 +15895,16 @@
     </row>
     <row r="7" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D7" t="s">
         <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F7">
         <v>40</v>
@@ -15933,34 +15913,34 @@
         <v>40</v>
       </c>
       <c r="H7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="I7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="K7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="L7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="M7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="N7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="O7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="P7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="Q7">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
@@ -16025,16 +16005,16 @@
     </row>
     <row r="8" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C8" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D8" t="s">
         <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F8">
         <v>26</v>
@@ -16043,34 +16023,34 @@
         <v>26</v>
       </c>
       <c r="H8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="I8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="K8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="M8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="N8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="O8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="P8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="Q8">
-        <v>26</v>
+        <v>26.780000000000005</v>
       </c>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
@@ -16135,16 +16115,16 @@
     </row>
     <row r="9" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C9" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D9" t="s">
         <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F9">
         <v>16</v>
@@ -16153,34 +16133,34 @@
         <v>16</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="I9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="J9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="K9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="L9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="N9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="O9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="P9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="Q9">
-        <v>16</v>
+        <v>16.48</v>
       </c>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
@@ -16245,10 +16225,10 @@
     </row>
     <row r="10" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D10" t="s">
         <v>91</v>
@@ -16263,34 +16243,34 @@
         <v>38.75</v>
       </c>
       <c r="H10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="I10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="J10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="K10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="L10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="M10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="N10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="O10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="P10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="Q10">
-        <v>38.75</v>
+        <v>39.912500000000001</v>
       </c>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
@@ -16355,16 +16335,16 @@
     </row>
     <row r="11" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C11" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D11" t="s">
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="F11">
         <v>27</v>
@@ -16373,34 +16353,34 @@
         <v>27</v>
       </c>
       <c r="H11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="I11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="J11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="K11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="L11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="M11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="N11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="O11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="P11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="Q11">
-        <v>27</v>
+        <v>27.81</v>
       </c>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
@@ -16465,16 +16445,16 @@
     </row>
     <row r="12" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C12" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="F12">
         <v>20</v>
@@ -16483,34 +16463,34 @@
         <v>20</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="I12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="J12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="K12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="L12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="M12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="N12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="O12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="P12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="Q12">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
@@ -16563,7 +16543,7 @@
     </row>
     <row r="13" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C13" t="s">
         <v>123</v>
@@ -16572,7 +16552,7 @@
         <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F13">
         <v>25</v>
@@ -16581,34 +16561,34 @@
         <v>25</v>
       </c>
       <c r="H13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="I13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="J13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="K13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="L13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="M13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="N13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="O13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="P13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="Q13">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
@@ -20123,7 +20103,7 @@
       <c r="H5" s="117"/>
       <c r="I5" s="118">
         <f>F5-SUM(F40:BN41)</f>
-        <v>51845.140000000014</v>
+        <v>43420.090000000084</v>
       </c>
       <c r="J5" s="104"/>
       <c r="K5" s="280" t="s">
@@ -20161,35 +20141,35 @@
       <c r="F7" s="113"/>
       <c r="G7" s="120" t="str">
         <f>IF(G8&gt;EOMONTH(FIN,0),"Fin",IF(G8&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="H7" s="120" t="str">
         <f t="shared" ref="H7:BN7" si="0">IF(H8&gt;EOMONTH(FIN,0),"Fin",IF(H8&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="I7" s="120" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="J7" s="120" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="K7" s="120" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="L7" s="120" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="M7" s="120" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="N7" s="120" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="O7" s="120" t="str">
         <f t="shared" si="0"/>
@@ -23645,43 +23625,43 @@
       </c>
       <c r="I40" s="124" cm="1">
         <f t="array" ref="I40">SUMPRODUCT(($D$10:$D$39="NO")*1,I$10:I$39,Resources!H7:H36)+I42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="J40" s="124" cm="1">
         <f t="array" ref="J40">SUMPRODUCT(($D$10:$D$39="NO")*1,J$10:J$39,Resources!I7:I36)+J42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="K40" s="124" cm="1">
         <f t="array" ref="K40">SUMPRODUCT(($D$10:$D$39="NO")*1,K$10:K$39,Resources!J7:J36)+K42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="L40" s="124" cm="1">
         <f t="array" ref="L40">SUMPRODUCT(($D$10:$D$39="NO")*1,L$10:L$39,Resources!K7:K36)+L42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="M40" s="124" cm="1">
         <f t="array" ref="M40">SUMPRODUCT(($D$10:$D$39="NO")*1,M$10:M$39,Resources!L7:L36)+M42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="N40" s="124" cm="1">
         <f t="array" ref="N40">SUMPRODUCT(($D$10:$D$39="NO")*1,N$10:N$39,Resources!M7:M36)+N42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="O40" s="124" cm="1">
         <f t="array" ref="O40">SUMPRODUCT(($D$10:$D$39="NO")*1,O$10:O$39,Resources!N7:N36)+O42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="P40" s="124" cm="1">
         <f t="array" ref="P40">SUMPRODUCT(($D$10:$D$39="NO")*1,P$10:P$39,Resources!O7:O36)+P42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="Q40" s="124" cm="1">
         <f t="array" ref="Q40">SUMPRODUCT(($D$10:$D$39="NO")*1,Q$10:Q$39,Resources!P7:P36)+Q42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="R40" s="124" cm="1">
         <f t="array" ref="R40">SUMPRODUCT(($D$10:$D$39="NO")*1,R$10:R$39,Resources!Q7:Q36)+R42</f>
-        <v>1840</v>
+        <v>1895.2</v>
       </c>
       <c r="S40" s="124" cm="1">
         <f t="array" ref="S40">SUMPRODUCT(($D$10:$D$39="NO")*1,S$10:S$39,Resources!R7:R36)+S42</f>
@@ -23894,43 +23874,43 @@
       </c>
       <c r="I41" s="124" cm="1">
         <f t="array" ref="I41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,I$10:I$39,Resources!H7:H36)+I43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="J41" s="124" cm="1">
         <f t="array" ref="J41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,J$10:J$39,Resources!I7:I36)+J43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="K41" s="124" cm="1">
         <f t="array" ref="K41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,K$10:K$39,Resources!J7:J36)+K43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="L41" s="124" cm="1">
         <f t="array" ref="L41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,L$10:L$39,Resources!K7:K36)+L43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="M41" s="124" cm="1">
         <f t="array" ref="M41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,M$10:M$39,Resources!L7:L36)+M43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="N41" s="124" cm="1">
         <f t="array" ref="N41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,N$10:N$39,Resources!M7:M36)+N43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="O41" s="124" cm="1">
         <f t="array" ref="O41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,O$10:O$39,Resources!N7:N36)+O43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="P41" s="124" cm="1">
         <f t="array" ref="P41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,P$10:P$39,Resources!O7:O36)+P43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="Q41" s="124" cm="1">
         <f t="array" ref="Q41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,Q$10:Q$39,Resources!P7:P36)+Q43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="R41" s="124" cm="1">
         <f t="array" ref="R41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,R$10:R$39,Resources!Q7:Q36)+R43</f>
-        <v>26243.5</v>
+        <v>27030.805</v>
       </c>
       <c r="S41" s="124" cm="1">
         <f t="array" ref="S41">SUMPRODUCT(($D$10:$D$39="INTERCO")*1,S$10:S$39,Resources!R7:R36)+S43</f>
@@ -25130,10 +25110,10 @@
         <v>145</v>
       </c>
       <c r="C53" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D53" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E53" s="236"/>
       <c r="F53" s="236"/>
@@ -25235,10 +25215,10 @@
         <v>146</v>
       </c>
       <c r="C54" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D54" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E54" s="236"/>
       <c r="F54" s="236"/>
@@ -26239,16 +26219,16 @@
     </row>
     <row r="64" spans="2:79" s="109" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C64" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D64" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E64" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="F64" s="11"/>
       <c r="G64">
@@ -28117,35 +28097,35 @@
       <c r="D4" s="149"/>
       <c r="E4" s="150" t="str">
         <f t="shared" ref="E4:BL4" si="0">IF(E5&gt;EOMONTH(FIN,0),"Fin",IF(E5&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="F4" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="G4" s="150" t="str">
         <f>IF(G5&gt;EOMONTH(FIN,0),"Fin",IF(G5&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="H4" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="I4" s="150" t="str">
         <f>IF(I5&gt;EOMONTH(FIN,0),"Fin",IF(I5&gt;FECHA,"Prev","Real"))</f>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="J4" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="K4" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="L4" s="150" t="str">
         <f t="shared" si="0"/>
-        <v>Real</v>
+        <v>Prev</v>
       </c>
       <c r="M4" s="150" t="str">
         <f t="shared" si="0"/>
@@ -31449,43 +31429,43 @@
       </c>
       <c r="G18" s="156">
         <f t="shared" ref="G18:AA18" ca="1" si="130">G30-F30</f>
-        <v>38842.13171549415</v>
+        <v>39977.479268045456</v>
       </c>
       <c r="H18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>38842.131715494121</v>
+        <v>39977.479268045456</v>
       </c>
       <c r="I18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>38842.13171549415</v>
+        <v>39977.479268045427</v>
       </c>
       <c r="J18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>38842.13171549415</v>
+        <v>39977.479268045456</v>
       </c>
       <c r="K18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>38842.131715494121</v>
+        <v>39977.479268045427</v>
       </c>
       <c r="L18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>38842.13171549415</v>
+        <v>39977.479268045456</v>
       </c>
       <c r="M18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>38842.13171549415</v>
+        <v>39977.479268045456</v>
       </c>
       <c r="N18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>38842.13171549415</v>
+        <v>39977.479268045456</v>
       </c>
       <c r="O18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>38842.131715494092</v>
+        <v>39977.479268045456</v>
       </c>
       <c r="P18" s="156">
         <f t="shared" ca="1" si="130"/>
-        <v>133470.80092570611</v>
+        <v>123252.67295274429</v>
       </c>
       <c r="Q18" s="156">
         <f t="shared" ca="1" si="130"/>
@@ -31677,7 +31657,7 @@
       </c>
       <c r="BL18" s="156">
         <f t="shared" ref="BL18:BL24" ca="1" si="167">BL30-BK30</f>
-        <v>-69865.760809347732</v>
+        <v>-58512.285283834673</v>
       </c>
       <c r="BM18" s="26"/>
       <c r="BN18" s="26"/>
@@ -31968,43 +31948,43 @@
       </c>
       <c r="G20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.004999999997</v>
       </c>
       <c r="H20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.005000000012</v>
       </c>
       <c r="I20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.005000000005</v>
       </c>
       <c r="J20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.005000000005</v>
       </c>
       <c r="K20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.005000000005</v>
       </c>
       <c r="L20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.005000000005</v>
       </c>
       <c r="M20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.005000000005</v>
       </c>
       <c r="N20" s="158">
         <f>N32-M32</f>
-        <v>28083.5</v>
+        <v>28926.005000000005</v>
       </c>
       <c r="O20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.005000000005</v>
       </c>
       <c r="P20" s="158">
         <f t="shared" si="170"/>
-        <v>28083.5</v>
+        <v>28926.005000000005</v>
       </c>
       <c r="Q20" s="158">
         <f t="shared" si="170"/>
@@ -33239,43 +33219,43 @@
       </c>
       <c r="G25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.004999999997</v>
       </c>
       <c r="H25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.005000000012</v>
       </c>
       <c r="I25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.005000000005</v>
       </c>
       <c r="J25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.005000000005</v>
       </c>
       <c r="K25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.005000000005</v>
       </c>
       <c r="L25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.005000000005</v>
       </c>
       <c r="M25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.005000000005</v>
       </c>
       <c r="N25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.005000000005</v>
       </c>
       <c r="O25" s="157">
         <f t="shared" si="175"/>
-        <v>28823.5</v>
+        <v>29666.005000000005</v>
       </c>
       <c r="P25" s="157">
         <f t="shared" si="175"/>
-        <v>47199.259999999995</v>
+        <v>48041.764999999999</v>
       </c>
       <c r="Q25" s="157">
         <f t="shared" si="175"/>
@@ -33486,43 +33466,43 @@
       </c>
       <c r="G26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.63171549415</v>
+        <v>10311.474268045458</v>
       </c>
       <c r="H26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.631715494121</v>
+        <v>10311.474268045444</v>
       </c>
       <c r="I26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.63171549415</v>
+        <v>10311.474268045422</v>
       </c>
       <c r="J26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.63171549415</v>
+        <v>10311.474268045451</v>
       </c>
       <c r="K26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.631715494121</v>
+        <v>10311.474268045422</v>
       </c>
       <c r="L26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.63171549415</v>
+        <v>10311.474268045451</v>
       </c>
       <c r="M26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.63171549415</v>
+        <v>10311.474268045451</v>
       </c>
       <c r="N26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.63171549415</v>
+        <v>10311.474268045451</v>
       </c>
       <c r="O26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>10018.631715494092</v>
+        <v>10311.474268045451</v>
       </c>
       <c r="P26" s="163">
         <f t="shared" ca="1" si="177"/>
-        <v>86271.540925706111</v>
+        <v>75210.907952744295</v>
       </c>
       <c r="Q26" s="163">
         <f t="shared" ca="1" si="177"/>
@@ -33714,7 +33694,7 @@
       </c>
       <c r="BL26" s="159">
         <f t="shared" ca="1" si="178"/>
-        <v>-69865.760809347732</v>
+        <v>-58512.285283834673</v>
       </c>
     </row>
     <row r="27" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33733,19 +33713,19 @@
       </c>
       <c r="G27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.2579320771804528</v>
+        <v>0.25793207718045297</v>
       </c>
       <c r="H27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045225</v>
+        <v>0.25793207718045258</v>
       </c>
       <c r="I27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.2579320771804528</v>
+        <v>0.25793207718045225</v>
       </c>
       <c r="J27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.2579320771804528</v>
+        <v>0.25793207718045275</v>
       </c>
       <c r="K27" s="160">
         <f t="shared" ca="1" si="179"/>
@@ -33753,23 +33733,23 @@
       </c>
       <c r="L27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.2579320771804528</v>
+        <v>0.25793207718045275</v>
       </c>
       <c r="M27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.2579320771804528</v>
+        <v>0.25793207718045275</v>
       </c>
       <c r="N27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.2579320771804528</v>
+        <v>0.25793207718045275</v>
       </c>
       <c r="O27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.25793207718045169</v>
+        <v>0.25793207718045275</v>
       </c>
       <c r="P27" s="160">
         <f t="shared" ca="1" si="179"/>
-        <v>0.6463701448358542</v>
+        <v>0.61021725655865122</v>
       </c>
       <c r="Q27" s="160">
         <f t="shared" ca="1" si="179"/>
@@ -34251,39 +34231,39 @@
       </c>
       <c r="G30" s="156" cm="1">
         <f t="array" aca="1" ref="G30" ca="1">IF(G40,G40,G6*((G32+G33+G34+G35+G36)/(IF(G14&lt;margendirectofinal,G6-G14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>139688.69535034086</v>
+        <v>140824.04290289216</v>
       </c>
       <c r="H30" s="156" cm="1">
         <f t="array" aca="1" ref="H30" ca="1">IF(H40,H40,H6*((H32+H33+H34+H35+H36)/(IF(H14&lt;margendirectofinal,H6-H14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>178530.82706583498</v>
+        <v>180801.52217093762</v>
       </c>
       <c r="I30" s="156" cm="1">
         <f t="array" aca="1" ref="I30" ca="1">IF(I40,I40,I6*((I32+I33+I34+I35+I36)/(IF(I14&lt;margendirectofinal,I6-I14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>217372.95878132913</v>
+        <v>220779.00143898305</v>
       </c>
       <c r="J30" s="156" cm="1">
         <f t="array" aca="1" ref="J30" ca="1">IF(J40,J40,J6*((J32+J33+J34+J35+J36)/(IF(J14&lt;margendirectofinal,J6-J14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>256215.09049682328</v>
+        <v>260756.4807070285</v>
       </c>
       <c r="K30" s="156" cm="1">
         <f t="array" aca="1" ref="K30" ca="1">IF(K40,K40,K6*((K32+K33+K34+K35+K36)/(IF(K14&lt;margendirectofinal,K6-K14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>295057.2222123174</v>
+        <v>300733.95997507393</v>
       </c>
       <c r="L30" s="156" cm="1">
         <f t="array" aca="1" ref="L30" ca="1">IF(L40,L40,L6*((L32+L33+L34+L35+L36)/(IF(L14&lt;margendirectofinal,L6-L14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>333899.35392781155</v>
+        <v>340711.43924311938</v>
       </c>
       <c r="M30" s="156" cm="1">
         <f t="array" aca="1" ref="M30" ca="1">IF(M40,M40,M6*((M32+M33+M34+M35+M36)/(IF(M14&lt;margendirectofinal,M6-M14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>372741.4856433057</v>
+        <v>380688.91851116484</v>
       </c>
       <c r="N30" s="156" cm="1">
         <f t="array" aca="1" ref="N30" ca="1">IF(N40,N40,N6*((N32+N33+N34+N35+N36)/(IF(N14&lt;margendirectofinal,N6-N14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>411583.61735879985</v>
+        <v>420666.3977792103</v>
       </c>
       <c r="O30" s="156" cm="1">
         <f t="array" aca="1" ref="O30" ca="1">IF(O40,O40,O6*((O32+O33+O34+O35+O36)/(IF(O14&lt;margendirectofinal,O6-O14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>450425.74907429394</v>
+        <v>460643.87704725575</v>
       </c>
       <c r="P30" s="156" cm="1">
         <f t="array" aca="1" ref="P30" ca="1">IF(P40,P40,P6*((P32+P33+P34+P35+P36)/(IF(P14&lt;margendirectofinal,P6-P14,pedidobaselineactual-margendirectofinal))))</f>
@@ -34479,7 +34459,7 @@
       </c>
       <c r="BL30" s="156" cm="1">
         <f t="array" aca="1" ref="BL30" ca="1">IF(BL40,BL40,BL6*((BL32+BL33+BL34+BL35+BL36)/(IF(BL14&lt;margendirectofinal,BL6-BL14,pedidobaselineactual-margendirectofinal))))</f>
-        <v>514030.78919065231</v>
+        <v>525384.26471616537</v>
       </c>
       <c r="BM30" s="26"/>
       <c r="BN30" s="26"/>
@@ -34776,235 +34756,235 @@
       </c>
       <c r="G32" s="164">
         <f>F32+LOOKUP(G$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(G$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>62918.5</v>
+        <v>63761.004999999997</v>
       </c>
       <c r="H32" s="164">
         <f>G32+LOOKUP(H$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(H$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>91002</v>
+        <v>92687.010000000009</v>
       </c>
       <c r="I32" s="164">
         <f>H32+LOOKUP(I$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(I$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>119085.5</v>
+        <v>121613.01500000001</v>
       </c>
       <c r="J32" s="164">
         <f>I32+LOOKUP(J$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(J$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>147169</v>
+        <v>150539.02000000002</v>
       </c>
       <c r="K32" s="164">
         <f>J32+LOOKUP(K$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(K$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>175252.5</v>
+        <v>179465.02500000002</v>
       </c>
       <c r="L32" s="164">
         <f>K32+LOOKUP(L$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(L$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>203336</v>
+        <v>208391.03000000003</v>
       </c>
       <c r="M32" s="164">
         <f>L32+LOOKUP(M$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(M$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>231419.5</v>
+        <v>237317.03500000003</v>
       </c>
       <c r="N32" s="164">
         <f>M32+LOOKUP(N$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(N$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>259503</v>
+        <v>266243.04000000004</v>
       </c>
       <c r="O32" s="164">
         <f>N32+LOOKUP(O$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(O$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>287586.5</v>
+        <v>295169.04500000004</v>
       </c>
       <c r="P32" s="164">
         <f>O32+LOOKUP(P$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(P$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="Q32" s="164">
         <f>P32+LOOKUP(Q$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(Q$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="R32" s="164">
         <f>Q32+LOOKUP(R$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(R$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="S32" s="164">
         <f>R32+LOOKUP(S$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(S$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="T32" s="164">
         <f>S32+LOOKUP(T$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(T$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="U32" s="164">
         <f>T32+LOOKUP(U$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(U$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="V32" s="164">
         <f>U32+LOOKUP(V$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(V$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="W32" s="164">
         <f>V32+LOOKUP(W$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(W$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="X32" s="164">
         <f>W32+LOOKUP(X$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(X$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="Y32" s="164">
         <f>X32+LOOKUP(Y$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(Y$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="Z32" s="164">
         <f>Y32+LOOKUP(Z$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(Z$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AA32" s="164">
         <f>Z32+LOOKUP(AA$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AA$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AB32" s="164">
         <f>AA32+LOOKUP(AB$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AB$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AC32" s="164">
         <f>AB32+LOOKUP(AC$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AC$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AD32" s="164">
         <f>AC32+LOOKUP(AD$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AD$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AE32" s="164">
         <f>AD32+LOOKUP(AE$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AE$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AF32" s="164">
         <f>AE32+LOOKUP(AF$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AF$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AG32" s="164">
         <f>AF32+LOOKUP(AG$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AG$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AH32" s="164">
         <f>AG32+LOOKUP(AH$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AH$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AI32" s="164">
         <f>AH32+LOOKUP(AI$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AI$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AJ32" s="164">
         <f>AI32+LOOKUP(AJ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AJ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AK32" s="164">
         <f>AJ32+LOOKUP(AK$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AK$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AL32" s="164">
         <f>AK32+LOOKUP(AL$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AL$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AM32" s="164">
         <f>AL32+LOOKUP(AM$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AM$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AN32" s="164">
         <f>AM32+LOOKUP(AN$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AN$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AO32" s="164">
         <f>AN32+LOOKUP(AO$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AO$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AP32" s="164">
         <f>AO32+LOOKUP(AP$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AP$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AQ32" s="164">
         <f>AP32+LOOKUP(AQ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AQ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AR32" s="164">
         <f>AQ32+LOOKUP(AR$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AR$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AS32" s="164">
         <f>AR32+LOOKUP(AS$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AS$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AT32" s="164">
         <f>AS32+LOOKUP(AT$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AT$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AU32" s="164">
         <f>AT32+LOOKUP(AU$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AU$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AV32" s="164">
         <f>AU32+LOOKUP(AV$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AV$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AW32" s="164">
         <f>AV32+LOOKUP(AW$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AW$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AX32" s="164">
         <f>AW32+LOOKUP(AX$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AX$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AY32" s="164">
         <f>AX32+LOOKUP(AY$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AY$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="AZ32" s="164">
         <f>AY32+LOOKUP(AZ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(AZ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BA32" s="164">
         <f>AZ32+LOOKUP(BA$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BA$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BB32" s="164">
         <f>BA32+LOOKUP(BB$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BB$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BC32" s="164">
         <f>BB32+LOOKUP(BC$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BC$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BD32" s="164">
         <f>BC32+LOOKUP(BD$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BD$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BE32" s="164">
         <f>BD32+LOOKUP(BE$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BE$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BF32" s="164">
         <f>BE32+LOOKUP(BF$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BF$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BG32" s="164">
         <f>BF32+LOOKUP(BG$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BG$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BH32" s="164">
         <f>BG32+LOOKUP(BH$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BH$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BI32" s="164">
         <f>BH32+LOOKUP(BI$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BI$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BJ32" s="164">
         <f>BI32+LOOKUP(BJ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BJ$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BK32" s="164">
         <f>BJ32+LOOKUP(BK$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BK$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BL32" s="164">
         <f>BK32+LOOKUP(BL$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$40:$BN$40)+LOOKUP(BL$5,'Cost Planning'!$G$8:$BN$8,'Cost Planning'!$G$41:$BN$41)</f>
-        <v>315670</v>
+        <v>324095.05000000005</v>
       </c>
       <c r="BN32" s="26"/>
       <c r="BO32" s="26"/>
@@ -36056,235 +36036,235 @@
       </c>
       <c r="G37" s="164">
         <f t="shared" si="240"/>
-        <v>103658.5</v>
+        <v>104501.005</v>
       </c>
       <c r="H37" s="164">
         <f t="shared" si="240"/>
-        <v>132482</v>
+        <v>134167.01</v>
       </c>
       <c r="I37" s="164">
         <f t="shared" si="240"/>
-        <v>161305.5</v>
+        <v>163833.01500000001</v>
       </c>
       <c r="J37" s="164">
         <f t="shared" si="240"/>
-        <v>190129</v>
+        <v>193499.02000000002</v>
       </c>
       <c r="K37" s="164">
         <f t="shared" si="240"/>
-        <v>218952.5</v>
+        <v>223165.02500000002</v>
       </c>
       <c r="L37" s="164">
         <f t="shared" si="240"/>
-        <v>247776</v>
+        <v>252831.03000000003</v>
       </c>
       <c r="M37" s="164">
         <f t="shared" si="240"/>
-        <v>276599.5</v>
+        <v>282497.03500000003</v>
       </c>
       <c r="N37" s="164">
         <f t="shared" si="240"/>
-        <v>305423</v>
+        <v>312163.04000000004</v>
       </c>
       <c r="O37" s="164">
         <f t="shared" si="240"/>
-        <v>334246.5</v>
+        <v>341829.04500000004</v>
       </c>
       <c r="P37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="Q37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="R37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="S37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="T37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="U37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="V37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="W37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="X37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="Y37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="Z37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AA37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AB37" s="164">
         <f t="shared" si="240"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AC37" s="164">
         <f t="shared" ref="AC37:BL37" si="241">SUM(AC32:AC36)</f>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AD37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AE37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AF37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AG37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AH37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AI37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AJ37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AK37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AL37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AM37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AN37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AO37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AP37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AQ37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AR37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AS37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AT37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AU37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AV37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AW37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AX37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AY37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="AZ37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BA37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BB37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BC37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BD37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BE37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BF37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BG37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BH37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BI37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BJ37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BK37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
       <c r="BL37" s="164">
         <f t="shared" si="241"/>
-        <v>381445.76</v>
+        <v>389870.81000000006</v>
       </c>
     </row>
     <row r="38" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
@@ -36306,235 +36286,235 @@
       </c>
       <c r="G38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>36030.195350340859</v>
+        <v>36323.03790289216</v>
       </c>
       <c r="H38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>46048.827065834979</v>
+        <v>46634.512170937611</v>
       </c>
       <c r="I38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>56067.458781329129</v>
+        <v>56945.986438983033</v>
       </c>
       <c r="J38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>66086.090496823279</v>
+        <v>67257.460707028484</v>
       </c>
       <c r="K38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>76104.7222123174</v>
+        <v>77568.934975073906</v>
       </c>
       <c r="L38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>86123.35392781155</v>
+        <v>87880.409243119357</v>
       </c>
       <c r="M38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>96141.985643305699</v>
+        <v>98191.883511164808</v>
       </c>
       <c r="N38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>106160.61735879985</v>
+        <v>108503.35777921026</v>
       </c>
       <c r="O38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>116179.24907429394</v>
+        <v>118814.83204725571</v>
       </c>
       <c r="P38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="Q38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="R38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="S38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="T38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="U38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="V38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="W38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="X38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="Y38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="Z38" s="165">
         <f t="shared" ca="1" si="242"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AA38" s="165">
         <f ca="1">AA30-AA32-AA33-AA34-AA35-AA36</f>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AB38" s="165">
         <f ca="1">AB30-AB32-AB33-AB34-AB35-AB36</f>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AC38" s="165">
         <f t="shared" ref="AC38:BL38" ca="1" si="243">AC30-AC32-AC33-AC34-AC35-AC36</f>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AD38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AE38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AF38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AG38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AH38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AI38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AJ38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AK38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AL38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AM38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AN38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AO38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AP38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AQ38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AR38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AS38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AT38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AU38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AV38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AW38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AX38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AY38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="AZ38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BA38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BB38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BC38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BD38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BE38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BF38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BG38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BH38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BI38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BJ38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BK38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>202450.79000000004</v>
+        <v>194025.74</v>
       </c>
       <c r="BL38" s="165">
         <f t="shared" ca="1" si="243"/>
-        <v>132585.02919065231</v>
+        <v>135513.45471616532</v>
       </c>
     </row>
     <row r="39" spans="2:77" x14ac:dyDescent="0.3">
@@ -37269,39 +37249,39 @@
       </c>
       <c r="G44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-139688.69535034086</v>
+        <v>-140824.04290289216</v>
       </c>
       <c r="H44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-178530.82706583498</v>
+        <v>-180801.52217093762</v>
       </c>
       <c r="I44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-217372.95878132913</v>
+        <v>-220779.00143898305</v>
       </c>
       <c r="J44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-256215.09049682328</v>
+        <v>-260756.4807070285</v>
       </c>
       <c r="K44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-295057.2222123174</v>
+        <v>-300733.95997507393</v>
       </c>
       <c r="L44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-333899.35392781155</v>
+        <v>-340711.43924311938</v>
       </c>
       <c r="M44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-372741.4856433057</v>
+        <v>-380688.91851116484</v>
       </c>
       <c r="N44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-411583.61735879985</v>
+        <v>-420666.3977792103</v>
       </c>
       <c r="O44" s="166">
         <f t="shared" ca="1" si="284"/>
-        <v>-450425.74907429394</v>
+        <v>-460643.87704725575</v>
       </c>
       <c r="P44" s="166">
         <f t="shared" ca="1" si="284"/>
@@ -37497,7 +37477,7 @@
       </c>
       <c r="BL44" s="166">
         <f t="shared" ca="1" si="285"/>
-        <v>-514030.78919065231</v>
+        <v>-525384.26471616537</v>
       </c>
       <c r="BN44" s="26"/>
       <c r="BO44" s="26"/>
@@ -39031,7 +39011,7 @@
       </c>
       <c r="E8" s="215">
         <f>SUM('Cost Planning'!F40:BN41)</f>
-        <v>315670</v>
+        <v>324095.04999999993</v>
       </c>
       <c r="F8" s="215">
         <f>SUM('Cost Planning'!F9:BN9)</f>
@@ -39055,19 +39035,19 @@
       </c>
       <c r="K8" s="215">
         <f>SUM(E8,G8,H8,I8,J8)</f>
-        <v>381445.76</v>
+        <v>389870.80999999994</v>
       </c>
       <c r="L8" s="215">
         <f>D8-K8</f>
-        <v>202450.79000000004</v>
+        <v>194025.74000000011</v>
       </c>
       <c r="M8" s="216">
         <f>IF(D8=0,0,(D8-E8-H8-I8-G8-J8)/D8)</f>
-        <v>0.34672373042793286</v>
+        <v>0.33229471898746465</v>
       </c>
       <c r="N8" s="216">
         <f>IF(D8=0,0,(D8-E8/UTILIZACION-G8/UTILIZACION-H8/UTILIZACION-I8-J8)/D8)</f>
-        <v>0.30366262782797443</v>
+        <v>0.28814756176295481</v>
       </c>
       <c r="O8" s="29"/>
       <c r="P8" s="27"/>
@@ -39083,7 +39063,7 @@
       </c>
       <c r="E9" s="217">
         <f t="shared" ref="E9:L9" si="0">IF(E8=0,1,(E8-E7)/E8)</f>
-        <v>-0.16423841353312008</v>
+        <v>-0.13397332048113691</v>
       </c>
       <c r="F9" s="217">
         <f t="shared" si="0"/>
@@ -39107,15 +39087,15 @@
       </c>
       <c r="K9" s="217">
         <f t="shared" si="0"/>
-        <v>-0.13591746307522204</v>
+        <v>-0.11137045628012031</v>
       </c>
       <c r="L9" s="217">
         <f t="shared" si="0"/>
-        <v>0.25608761516811074</v>
+        <v>0.22378520499393564</v>
       </c>
       <c r="M9" s="218">
         <f>M8-M7</f>
-        <v>8.8791653247480229E-2</v>
+        <v>7.436264180701202E-2</v>
       </c>
       <c r="N9" s="239"/>
       <c r="O9" s="29"/>
@@ -39144,16 +39124,16 @@
       </c>
       <c r="C11" s="292"/>
       <c r="D11" s="208">
-        <f ca="1">SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$18:$BL$18)+'Project Infor'!C45</f>
-        <v>333899.35392781155</v>
+        <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$18:$BL$18)+'Project Infor'!C45</f>
+        <v>0</v>
       </c>
       <c r="E11" s="208">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$20:$BL$20)+'Project Infor'!C47</f>
-        <v>203336</v>
+        <v>0</v>
       </c>
       <c r="F11" s="208">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$19:$BL$19)+'Project Infor'!C46</f>
-        <v>7598</v>
+        <v>0</v>
       </c>
       <c r="G11" s="208">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$21:$BL$21)</f>
@@ -39165,27 +39145,27 @@
       </c>
       <c r="I11" s="208">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$23:$BL$23)+'Project Infor'!C48</f>
-        <v>4440</v>
+        <v>0</v>
       </c>
       <c r="J11" s="208">
         <f>SUMIF('Monthly View'!$E$4:$BL$4,"Real",'Monthly View'!$E$24:$BL$24)+'Project Infor'!C49</f>
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="K11" s="208">
         <f>SUM(E11,G11,H11,I11,J11)</f>
-        <v>247776</v>
+        <v>0</v>
       </c>
       <c r="L11" s="208">
-        <f ca="1">D11-K11</f>
-        <v>86123.35392781155</v>
+        <f>D11-K11</f>
+        <v>0</v>
       </c>
       <c r="M11" s="209">
-        <f ca="1">IF(D11=0,0,(D11-E11-H11-I11-G11-J11)/D11)</f>
-        <v>0.25793207718045258</v>
+        <f>IF(D11=0,0,(D11-E11-H11-I11-G11-J11)/D11)</f>
+        <v>0</v>
       </c>
       <c r="N11" s="207">
-        <f ca="1">IF(D11=0,0,(D11-E11/UTILIZACION-G11/UTILIZACION-H11/UTILIZACION-I11-J11)/D11)</f>
-        <v>0.21209533016367751</v>
+        <f>IF(D11=0,0,(D11-E11/UTILIZACION-G11/UTILIZACION-H11/UTILIZACION-I11-J11)/D11)</f>
+        <v>0</v>
       </c>
       <c r="O11" s="29"/>
       <c r="P11" s="27"/>
@@ -39196,16 +39176,16 @@
       </c>
       <c r="C12" s="290"/>
       <c r="D12" s="171">
-        <f ca="1">IF(D11=0,1,(D11/D8))</f>
-        <v>0.57184676622564656</v>
+        <f>IF(D8=0,0,D11/D8)</f>
+        <v>0</v>
       </c>
       <c r="E12" s="171">
-        <f>IF(E11=0,1,(E11/E8))</f>
-        <v>0.6441410333576203</v>
+        <f>IF(E8=0,0,E11/E8)</f>
+        <v>0</v>
       </c>
       <c r="F12" s="171">
-        <f>IF(F11=0,1,(F11/F8))</f>
-        <v>0.64118143459915611</v>
+        <f>IF(F8=0,0,F11/F8)</f>
+        <v>0</v>
       </c>
       <c r="G12" s="171"/>
       <c r="H12" s="171"/>
@@ -39239,7 +39219,7 @@
     </row>
     <row r="18" spans="2:16" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="287" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C18" s="288"/>
       <c r="D18" s="288"/>
@@ -41512,12 +41492,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005104B4C06FD53E4DA82687A05841D03F" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="baecee92fc6a23d7c0a643ff746a4af3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7dc5af80-ab8f-4cff-b7cb-3463b3238b39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec4a10ea1a6ac0e8b531773a0b4fa9ce" ns2:_="">
     <xsd:import namespace="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
@@ -41691,6 +41665,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E2031B-F3FA-42B6-8826-6D4F98BAE269}">
   <ds:schemaRefs>
@@ -41700,22 +41680,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826E8F03-94FF-4994-AD38-2615BDB97036}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E82769-0714-4D10-A15E-4D1316028E66}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41733,6 +41697,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826E8F03-94FF-4994-AD38-2615BDB97036}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{040b5de6-6e2e-46f2-bca1-507eb809bbf7}" enabled="1" method="Privileged" siteId="{56d7daaa-b378-45b3-aa11-af9402b401b9}" contentBits="0" removed="0"/>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.36-e08\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.37-e08-review\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1F30C8-CE9B-4996-9BDF-2AA807FA729A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14336D1F-DDF0-4055-93D6-7193CA0DE83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="306">
   <si>
     <t xml:space="preserve">CORE (COst REport) - PC </t>
   </si>
@@ -575,9 +575,6 @@
     <t>PENDIENTE DE PLANIFICAR</t>
   </si>
   <si>
-    <t>(!) El coste de RECURSOS planificado es mayor que el de la BASELINE</t>
-  </si>
-  <si>
     <t>CODIGO INTERCO</t>
   </si>
   <si>
@@ -611,9 +608,6 @@
     <t>COSTE TOTAL GASTOS BASELINE</t>
   </si>
   <si>
-    <t>(!) El coste de GASTOS planificado es mayor que el de la BASELINE</t>
-  </si>
-  <si>
     <t>TIPO GASTO</t>
   </si>
   <si>
@@ -636,9 +630,6 @@
   </si>
   <si>
     <t xml:space="preserve">COSTE TOTAL COMPRAS BASELINE </t>
-  </si>
-  <si>
-    <t>(!) El coste de COMPRAS planificado es mayor que el de la BASELINE</t>
   </si>
   <si>
     <t>PROVEEDOR</t>
@@ -1052,6 +1043,9 @@
     <t>Smart Airport en la nueva terminal de Puerto Vallarta</t>
   </si>
   <si>
+    <t>Compania: Connectis-ICT | Unidad: ICT | Portfolio: Smart Spaces | Subpractice: Smart Spaces/EAI | Origen: Mobility</t>
+  </si>
+  <si>
     <t>GAP</t>
   </si>
   <si>
@@ -1145,7 +1139,7 @@
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>Generado por RPA: 2026-05-11 10:17:02 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | ADVERTENCIA: PPO contiene anualidades de horas fuera del periodo CORE planificado.</t>
+    <t>Generado por RPA: 2026-05-11 10:45:50 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | ADVERTENCIA: PPO contiene anualidades de horas fuera del periodo CORE planificado.</t>
   </si>
 </sst>
 </file>
@@ -7590,7 +7584,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="234" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D10" s="235"/>
       <c r="H10" s="29"/>
@@ -7608,7 +7602,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="302" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D11" s="302"/>
       <c r="E11" s="302"/>
@@ -7646,7 +7640,9 @@
       <c r="B13" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="300"/>
+      <c r="C13" s="300" t="s">
+        <v>273</v>
+      </c>
       <c r="D13" s="301"/>
       <c r="H13" s="29"/>
       <c r="I13" s="29"/>
@@ -7701,7 +7697,7 @@
         <v>461530</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="29"/>
@@ -7738,7 +7734,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D18" s="16"/>
       <c r="E18" s="29"/>
@@ -7821,7 +7817,7 @@
         <v>3900331</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E22" s="75"/>
       <c r="F22" s="187"/>
@@ -7844,7 +7840,7 @@
         <v>3659518</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E23" s="75"/>
       <c r="F23" s="187"/>
@@ -7867,7 +7863,7 @@
         <v>458354</v>
       </c>
       <c r="D24" s="184" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E24" s="75"/>
       <c r="F24" s="187"/>
@@ -8570,7 +8566,7 @@
     </row>
     <row r="61" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="26" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C61" s="29"/>
       <c r="D61" s="29"/>
@@ -8589,7 +8585,7 @@
     </row>
     <row r="62" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="26" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
@@ -8608,12 +8604,12 @@
     </row>
     <row r="63" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" s="26" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="64" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="26" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C64" s="29"/>
       <c r="D64" s="29"/>
@@ -8637,7 +8633,7 @@
     </row>
     <row r="66" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="26" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -8671,7 +8667,7 @@
     </row>
     <row r="70" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" s="26" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -8724,7 +8720,7 @@
     </row>
     <row r="75" spans="2:16" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="26" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C75" s="29"/>
       <c r="D75" s="29"/>
@@ -8841,28 +8837,28 @@
     </row>
     <row r="4" spans="2:23" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="82" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C4" s="299" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D4" s="299"/>
       <c r="E4" s="27"/>
       <c r="F4" s="316" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G4" s="317"/>
       <c r="H4" s="242" t="s">
+        <v>230</v>
+      </c>
+      <c r="I4" s="242" t="s">
+        <v>231</v>
+      </c>
+      <c r="J4" s="242" t="s">
+        <v>232</v>
+      </c>
+      <c r="K4" s="316" t="s">
         <v>233</v>
-      </c>
-      <c r="I4" s="242" t="s">
-        <v>234</v>
-      </c>
-      <c r="J4" s="242" t="s">
-        <v>235</v>
-      </c>
-      <c r="K4" s="316" t="s">
-        <v>236</v>
       </c>
       <c r="L4" s="316"/>
       <c r="M4" s="316"/>
@@ -8870,15 +8866,15 @@
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="82" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C5" s="314" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D5" s="314"/>
       <c r="E5" s="27"/>
       <c r="F5" s="314" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G5" s="314"/>
       <c r="H5" s="244">
@@ -8888,7 +8884,7 @@
         <v>5000</v>
       </c>
       <c r="J5" s="234" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K5" s="314"/>
       <c r="L5" s="314"/>
@@ -8897,15 +8893,15 @@
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="82" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C6" s="314" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D6" s="314"/>
       <c r="E6" s="27"/>
       <c r="F6" s="314" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G6" s="314"/>
       <c r="H6" s="244">
@@ -8922,17 +8918,17 @@
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="82" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C7" s="315">
         <v>10000</v>
       </c>
       <c r="D7" s="315"/>
       <c r="E7" s="243" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F7" s="314" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G7" s="314"/>
       <c r="H7" s="244">
@@ -8951,7 +8947,7 @@
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="314" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G8" s="314"/>
       <c r="H8" s="244">
@@ -8970,7 +8966,7 @@
       <c r="D9" s="27"/>
       <c r="E9" s="61"/>
       <c r="F9" s="314" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G9" s="314"/>
       <c r="H9" s="244">
@@ -8989,7 +8985,7 @@
     </row>
     <row r="10" spans="2:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="318" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D10" s="318"/>
       <c r="M10" s="29"/>
@@ -9013,46 +9009,46 @@
     </row>
     <row r="12" spans="2:23" s="91" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="47" t="s">
+        <v>209</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="F12" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="47" t="s">
-        <v>248</v>
-      </c>
-      <c r="E12" s="47" t="s">
+      <c r="G12" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="H12" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="I12" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="G12" s="48" t="s">
-        <v>217</v>
-      </c>
-      <c r="H12" s="47" t="s">
+      <c r="J12" s="47" t="s">
         <v>218</v>
       </c>
-      <c r="I12" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="J12" s="47" t="s">
+      <c r="K12" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="L12" s="48" t="s">
+        <v>220</v>
+      </c>
+      <c r="M12" s="48" t="s">
         <v>221</v>
       </c>
-      <c r="K12" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="L12" s="48" t="s">
+      <c r="N12" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="O12" s="48" t="s">
         <v>223</v>
-      </c>
-      <c r="M12" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="N12" s="48" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" s="48" t="s">
-        <v>226</v>
       </c>
       <c r="P12" s="29"/>
       <c r="Q12" s="26"/>
@@ -9065,22 +9061,22 @@
     </row>
     <row r="13" spans="2:23" s="72" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="205" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C13" s="232">
         <v>44286</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F13" s="5">
         <v>3000</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H13" s="13">
         <v>0.21</v>
@@ -9090,12 +9086,12 @@
         <v>3630</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="60"/>
       <c r="M13" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -10070,7 +10066,7 @@
     </row>
     <row r="46" spans="2:23" s="94" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="311" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C46" s="311"/>
       <c r="D46" s="311"/>
@@ -10218,7 +10214,7 @@
     <row r="53" spans="2:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="55" spans="2:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="70" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C55" s="70"/>
       <c r="D55" s="70"/>
@@ -10365,11 +10361,11 @@
     </row>
     <row r="5" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="319" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C5" s="319"/>
       <c r="D5" s="320" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E5" s="320"/>
       <c r="F5" s="320"/>
@@ -10388,10 +10384,10 @@
     </row>
     <row r="6" spans="1:41" s="108" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="237" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C6" s="237" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D6" s="248">
         <f>'Project Infor'!$C$8</f>
@@ -10777,7 +10773,7 @@
     <row r="12" spans="1:41" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="276"/>
       <c r="C12" s="276" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D12" s="277">
         <f>SUMPRODUCT(D7:D11,$B$7:$B$11)</f>
@@ -10924,11 +10920,11 @@
     </row>
     <row r="15" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="319" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C15" s="319"/>
       <c r="D15" s="320" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E15" s="320"/>
       <c r="F15" s="320"/>
@@ -10947,10 +10943,10 @@
     </row>
     <row r="16" spans="1:41" s="108" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="237" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C16" s="237" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D16" s="248">
         <f>'Project Infor'!$C$8</f>
@@ -11293,7 +11289,7 @@
     <row r="22" spans="1:41" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="276"/>
       <c r="C22" s="276" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D22" s="277">
         <f t="shared" ref="D22:AB22" si="47">SUMPRODUCT(D17:D21,$B$17:$B$21)</f>
@@ -11440,11 +11436,11 @@
     </row>
     <row r="25" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="319" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C25" s="319"/>
       <c r="D25" s="320" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E25" s="320"/>
       <c r="F25" s="320"/>
@@ -11463,10 +11459,10 @@
     </row>
     <row r="26" spans="1:41" s="108" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="237" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C26" s="237" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D26" s="248">
         <f>'Project Infor'!$C$8</f>
@@ -11823,7 +11819,7 @@
     <row r="32" spans="1:41" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="276"/>
       <c r="C32" s="276" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D32" s="277">
         <f t="shared" ref="D32:AB32" si="73">SUMPRODUCT(D27:D31,$B$27:$B$31)</f>
@@ -11970,11 +11966,11 @@
     </row>
     <row r="35" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="319" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C35" s="319"/>
       <c r="D35" s="320" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E35" s="320"/>
       <c r="F35" s="320"/>
@@ -11993,10 +11989,10 @@
     </row>
     <row r="36" spans="1:41" s="108" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="237" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C36" s="237" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D36" s="248">
         <f>'Project Infor'!$C$8</f>
@@ -12337,7 +12333,7 @@
     <row r="42" spans="1:41" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="276"/>
       <c r="C42" s="276" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D42" s="277">
         <f t="shared" ref="D42:AB42" si="99">SUMPRODUCT(D37:D41,$B$37:$B$41)</f>
@@ -12484,11 +12480,11 @@
     </row>
     <row r="45" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="319" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C45" s="319"/>
       <c r="D45" s="320" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E45" s="320"/>
       <c r="F45" s="320"/>
@@ -12507,10 +12503,10 @@
     </row>
     <row r="46" spans="1:41" s="108" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="237" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C46" s="237" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D46" s="248">
         <f>'Project Infor'!$C$8</f>
@@ -12851,7 +12847,7 @@
     <row r="52" spans="1:41" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="276"/>
       <c r="C52" s="276" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D52" s="277">
         <f>SUMPRODUCT(D47:D51,$B$47:$B$51)</f>
@@ -12998,11 +12994,11 @@
     </row>
     <row r="55" spans="1:41" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="319" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C55" s="319"/>
       <c r="D55" s="320" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E55" s="320"/>
       <c r="F55" s="320"/>
@@ -13021,10 +13017,10 @@
     </row>
     <row r="56" spans="1:41" s="108" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="237" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C56" s="237" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D56" s="248">
         <f>'Project Infor'!$C$8</f>
@@ -13356,7 +13352,7 @@
     <row r="62" spans="1:41" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="276"/>
       <c r="C62" s="276" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D62" s="277">
         <f>SUMPRODUCT(D57:D61,$B$57:$B$61)</f>
@@ -15895,16 +15891,16 @@
     </row>
     <row r="7" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D7" t="s">
         <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F7">
         <v>40</v>
@@ -16005,16 +16001,16 @@
     </row>
     <row r="8" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D8" t="s">
         <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F8">
         <v>26</v>
@@ -16115,16 +16111,16 @@
     </row>
     <row r="9" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D9" t="s">
         <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F9">
         <v>16</v>
@@ -16225,10 +16221,10 @@
     </row>
     <row r="10" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D10" t="s">
         <v>91</v>
@@ -16335,16 +16331,16 @@
     </row>
     <row r="11" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D11" t="s">
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F11">
         <v>27</v>
@@ -16445,16 +16441,16 @@
     </row>
     <row r="12" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C12" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F12">
         <v>20</v>
@@ -16543,7 +16539,7 @@
     </row>
     <row r="13" spans="2:78" s="109" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C13" t="s">
         <v>123</v>
@@ -16552,7 +16548,7 @@
         <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F13">
         <v>25</v>
@@ -20102,12 +20098,13 @@
       </c>
       <c r="H5" s="117"/>
       <c r="I5" s="118">
-        <f>F5-SUM(F40:BN41)</f>
-        <v>43420.090000000084</v>
+        <f>ROUND(F5-SUM(F40:BN41),2)</f>
+        <v>43420.09</v>
       </c>
       <c r="J5" s="104"/>
-      <c r="K5" s="280" t="s">
-        <v>128</v>
+      <c r="K5" s="280" t="str">
+        <f>IF(I5&lt;-0.005,"(!) El coste de RECURSOS planificado es mayor que el de la BASELINE","")</f>
+        <v/>
       </c>
       <c r="L5" s="280"/>
       <c r="M5" s="280"/>
@@ -20394,7 +20391,7 @@
         <v>92</v>
       </c>
       <c r="F8" s="106" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G8" s="107">
         <v>45962</v>
@@ -20640,7 +20637,7 @@
     </row>
     <row r="9" spans="2:79" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="121" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="122"/>
       <c r="D9" s="123"/>
@@ -23606,7 +23603,7 @@
     </row>
     <row r="40" spans="2:79" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C40" s="122"/>
       <c r="D40" s="123"/>
@@ -23858,7 +23855,7 @@
     </row>
     <row r="41" spans="2:79" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="126" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C41" s="127"/>
       <c r="D41" s="128"/>
@@ -24108,7 +24105,7 @@
     <row r="42" spans="2:79" s="109" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="238"/>
       <c r="C42" s="281" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D42" s="281"/>
       <c r="E42" s="281"/>
@@ -24177,7 +24174,7 @@
     <row r="43" spans="2:79" s="109" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="238"/>
       <c r="C43" s="238" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D43" s="238"/>
       <c r="E43" s="238"/>
@@ -24331,7 +24328,7 @@
       <c r="B46" s="103"/>
       <c r="C46" s="131"/>
       <c r="D46" s="131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E46" s="132" t="s">
         <v>127</v>
@@ -24596,7 +24593,7 @@
         <v>61</v>
       </c>
       <c r="C47" s="134" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D47" s="135">
         <f>'Cost Overview'!I8</f>
@@ -24684,10 +24681,10 @@
     </row>
     <row r="48" spans="2:79" s="109" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" s="139" t="s">
         <v>137</v>
-      </c>
-      <c r="C48" s="139" t="s">
-        <v>138</v>
       </c>
       <c r="D48" s="140">
         <f>'Cost Overview'!J8</f>
@@ -24796,7 +24793,7 @@
       </c>
       <c r="C50" s="104"/>
       <c r="D50" s="115" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E50" s="115"/>
       <c r="F50" s="116">
@@ -24808,12 +24805,13 @@
       </c>
       <c r="H50" s="117"/>
       <c r="I50" s="118">
-        <f>F50-SUM(F59:BN59)</f>
+        <f>ROUND(F50-SUM(F59:BN59),2)</f>
         <v>0</v>
       </c>
       <c r="J50" s="104"/>
-      <c r="K50" s="280" t="s">
-        <v>140</v>
+      <c r="K50" s="280" t="str">
+        <f>IF(I50&lt;-0.005,"(!) El coste de GASTOS planificado es mayor que el de la BASELINE","")</f>
+        <v/>
       </c>
       <c r="L50" s="280"/>
       <c r="M50" s="280"/>
@@ -24841,13 +24839,13 @@
     </row>
     <row r="52" spans="2:79" s="108" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="237" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" s="237" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="237" t="s">
         <v>141</v>
-      </c>
-      <c r="C52" s="237" t="s">
-        <v>142</v>
-      </c>
-      <c r="D52" s="237" t="s">
-        <v>143</v>
       </c>
       <c r="E52" s="237"/>
       <c r="F52" s="106"/>
@@ -25107,13 +25105,13 @@
     </row>
     <row r="53" spans="2:79" s="109" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C53" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D53" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E53" s="236"/>
       <c r="F53" s="236"/>
@@ -25212,13 +25210,13 @@
     </row>
     <row r="54" spans="2:79" s="109" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C54" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D54" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E54" s="236"/>
       <c r="F54" s="236"/>
@@ -25633,7 +25631,7 @@
     </row>
     <row r="59" spans="2:79" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="121" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C59" s="122"/>
       <c r="D59" s="123"/>
@@ -25906,7 +25904,7 @@
       </c>
       <c r="C61" s="104"/>
       <c r="D61" s="115" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E61" s="115"/>
       <c r="F61" s="116">
@@ -25918,12 +25916,13 @@
       </c>
       <c r="H61" s="143"/>
       <c r="I61" s="118">
-        <f>F61-SUM(F74:BN74)</f>
+        <f>ROUND(F61-SUM(F74:BN74),2)</f>
         <v>0</v>
       </c>
       <c r="J61" s="104"/>
-      <c r="K61" s="280" t="s">
-        <v>149</v>
+      <c r="K61" s="280" t="str">
+        <f>IF(I61&lt;-0.005,"(!) El coste de COMPRAS planificado es mayor que el de la BASELINE","")</f>
+        <v/>
       </c>
       <c r="L61" s="280"/>
       <c r="M61" s="280"/>
@@ -25951,16 +25950,16 @@
     </row>
     <row r="63" spans="2:79" s="108" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="237" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="237" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" s="237" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" s="237" t="s">
         <v>150</v>
-      </c>
-      <c r="C63" s="237" t="s">
-        <v>151</v>
-      </c>
-      <c r="D63" s="237" t="s">
-        <v>152</v>
-      </c>
-      <c r="E63" s="237" t="s">
-        <v>153</v>
       </c>
       <c r="F63" s="106"/>
       <c r="G63" s="107">
@@ -26219,16 +26218,16 @@
     </row>
     <row r="64" spans="2:79" s="109" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
+        <v>301</v>
+      </c>
+      <c r="C64" t="s">
+        <v>302</v>
+      </c>
+      <c r="D64" t="s">
         <v>303</v>
       </c>
-      <c r="C64" t="s">
+      <c r="E64" t="s">
         <v>304</v>
-      </c>
-      <c r="D64" t="s">
-        <v>305</v>
-      </c>
-      <c r="E64" t="s">
-        <v>306</v>
       </c>
       <c r="F64" s="11"/>
       <c r="G64">
@@ -27021,7 +27020,7 @@
     </row>
     <row r="74" spans="2:79" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="144" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C74" s="145"/>
       <c r="D74" s="145"/>
@@ -27552,37 +27551,37 @@
     </row>
     <row r="85" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B85" s="147" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="86" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B86" s="26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B87" s="26" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B88" s="26" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="89" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B89" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B90" s="26" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="14" x14ac:dyDescent="0.3">
       <c r="B91" s="26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="2:2" ht="14" x14ac:dyDescent="0.3">
@@ -28338,11 +28337,11 @@
     </row>
     <row r="5" spans="2:77" s="91" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="237" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C5" s="237"/>
       <c r="D5" s="151" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E5" s="152">
         <v>45962</v>
@@ -28588,7 +28587,7 @@
     </row>
     <row r="6" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="282" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C6" s="282"/>
       <c r="D6" s="155">
@@ -29113,7 +29112,7 @@
     </row>
     <row r="8" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B8" s="283" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C8" s="283"/>
       <c r="D8" s="157">
@@ -29375,7 +29374,7 @@
     </row>
     <row r="9" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B9" s="283" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C9" s="283"/>
       <c r="D9" s="157">
@@ -29637,7 +29636,7 @@
     </row>
     <row r="10" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B10" s="283" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C10" s="283"/>
       <c r="D10" s="157">
@@ -29899,7 +29898,7 @@
     </row>
     <row r="11" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B11" s="283" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="283"/>
       <c r="D11" s="157">
@@ -30149,7 +30148,7 @@
     </row>
     <row r="12" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B12" s="283" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C12" s="283"/>
       <c r="D12" s="157">
@@ -30649,7 +30648,7 @@
     </row>
     <row r="14" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="284" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C14" s="284"/>
       <c r="D14" s="159">
@@ -30899,7 +30898,7 @@
     </row>
     <row r="15" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="284" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C15" s="284"/>
       <c r="D15" s="160">
@@ -31155,7 +31154,7 @@
     </row>
     <row r="17" spans="2:77" s="91" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="237" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C17" s="237"/>
       <c r="D17" s="161"/>
@@ -31415,7 +31414,7 @@
     </row>
     <row r="18" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="282" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C18" s="282"/>
       <c r="D18" s="156"/>
@@ -31934,7 +31933,7 @@
     </row>
     <row r="20" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B20" s="283" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C20" s="283"/>
       <c r="D20" s="158"/>
@@ -32193,7 +32192,7 @@
     </row>
     <row r="21" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B21" s="283" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C21" s="283"/>
       <c r="D21" s="158"/>
@@ -32452,7 +32451,7 @@
     </row>
     <row r="22" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B22" s="283" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C22" s="283"/>
       <c r="D22" s="158"/>
@@ -32711,7 +32710,7 @@
     </row>
     <row r="23" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B23" s="283" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C23" s="283"/>
       <c r="D23" s="158"/>
@@ -32958,7 +32957,7 @@
     </row>
     <row r="24" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B24" s="283" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C24" s="283"/>
       <c r="D24" s="158"/>
@@ -33452,7 +33451,7 @@
     </row>
     <row r="26" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="285" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C26" s="285"/>
       <c r="D26" s="159"/>
@@ -33699,7 +33698,7 @@
     </row>
     <row r="27" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="285" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C27" s="285"/>
       <c r="D27" s="160"/>
@@ -33952,11 +33951,11 @@
     </row>
     <row r="29" spans="2:77" s="91" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="237" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C29" s="237"/>
       <c r="D29" s="151" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E29" s="162">
         <f>'Project Infor'!C8</f>
@@ -34214,7 +34213,7 @@
     </row>
     <row r="30" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="282" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C30" s="282"/>
       <c r="D30" s="156">
@@ -34739,7 +34738,7 @@
     </row>
     <row r="32" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B32" s="283" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C32" s="283"/>
       <c r="D32" s="164">
@@ -35001,7 +35000,7 @@
     </row>
     <row r="33" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="283" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C33" s="283"/>
       <c r="D33" s="164"/>
@@ -35260,7 +35259,7 @@
     </row>
     <row r="34" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" s="283" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C34" s="283"/>
       <c r="D34" s="164"/>
@@ -35519,7 +35518,7 @@
     </row>
     <row r="35" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" s="283" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C35" s="283"/>
       <c r="D35" s="164">
@@ -35769,7 +35768,7 @@
     </row>
     <row r="36" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B36" s="283" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C36" s="283"/>
       <c r="D36" s="164">
@@ -36269,7 +36268,7 @@
     </row>
     <row r="38" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="284" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C38" s="284"/>
       <c r="D38" s="165">
@@ -36581,7 +36580,7 @@
     </row>
     <row r="40" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="286" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C40" s="286"/>
       <c r="D40" s="167"/>
@@ -36903,7 +36902,7 @@
     </row>
     <row r="42" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="286" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C42" s="286"/>
       <c r="D42" s="167">
@@ -36985,7 +36984,7 @@
     </row>
     <row r="43" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="285" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C43" s="285"/>
       <c r="D43" s="159">
@@ -37235,7 +37234,7 @@
     </row>
     <row r="44" spans="2:77" s="72" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="285" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C44" s="285"/>
       <c r="D44" s="166"/>
@@ -38885,10 +38884,10 @@
         <v>65</v>
       </c>
       <c r="L5" s="211" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M5" s="214" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="N5" s="214" t="s">
         <v>67</v>
@@ -38898,7 +38897,7 @@
     </row>
     <row r="6" spans="2:16" s="94" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="291" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C6" s="292"/>
       <c r="D6" s="208">
@@ -38950,7 +38949,7 @@
     </row>
     <row r="7" spans="2:16" s="94" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="293" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C7" s="293"/>
       <c r="D7" s="215">
@@ -39002,7 +39001,7 @@
     </row>
     <row r="8" spans="2:16" s="94" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="293" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C8" s="293"/>
       <c r="D8" s="215">
@@ -39054,43 +39053,43 @@
     </row>
     <row r="9" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="294" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C9" s="294"/>
       <c r="D9" s="217">
-        <f>IF(D8=0,1,(D8-D7)/D8)</f>
+        <f>IF(AND(D8=0,D7=0),0,IF(D8=0,1,(D8-D7)/D8))</f>
         <v>0</v>
       </c>
       <c r="E9" s="217">
-        <f t="shared" ref="E9:L9" si="0">IF(E8=0,1,(E8-E7)/E8)</f>
+        <f>IF(AND(E8=0,E7=0),0,IF(E8=0,1,(E8-E7)/E8))</f>
         <v>-0.13397332048113691</v>
       </c>
       <c r="F9" s="217">
-        <f t="shared" si="0"/>
+        <f>IF(AND(F8=0,F7=0),0,IF(F8=0,1,(F8-F7)/F8))</f>
         <v>-0.1451476793248945</v>
       </c>
       <c r="G9" s="217">
-        <f t="shared" si="0"/>
+        <f>IF(AND(G8=0,G7=0),0,IF(G8=0,1,(G8-G7)/G8))</f>
         <v>0</v>
       </c>
       <c r="H9" s="217">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF(AND(H8=0,H7=0),0,IF(H8=0,1,(H8-H7)/H8))</f>
+        <v>0</v>
       </c>
       <c r="I9" s="217">
-        <f t="shared" si="0"/>
+        <f>IF(AND(I8=0,I7=0),0,IF(I8=0,1,(I8-I7)/I8))</f>
         <v>0</v>
       </c>
       <c r="J9" s="217">
-        <f t="shared" si="0"/>
+        <f>IF(AND(J8=0,J7=0),0,IF(J8=0,1,(J8-J7)/J8))</f>
         <v>0</v>
       </c>
       <c r="K9" s="217">
-        <f t="shared" si="0"/>
+        <f>IF(AND(K8=0,K7=0),0,IF(K8=0,1,(K8-K7)/K8))</f>
         <v>-0.11137045628012031</v>
       </c>
       <c r="L9" s="217">
-        <f t="shared" si="0"/>
+        <f>IF(AND(L8=0,L7=0),0,IF(L8=0,1,(L8-L7)/L8))</f>
         <v>0.22378520499393564</v>
       </c>
       <c r="M9" s="218">
@@ -39120,7 +39119,7 @@
     </row>
     <row r="11" spans="2:16" s="94" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="292" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C11" s="292"/>
       <c r="D11" s="208">
@@ -39172,7 +39171,7 @@
     </row>
     <row r="12" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="290" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C12" s="290"/>
       <c r="D12" s="171">
@@ -39200,7 +39199,7 @@
     </row>
     <row r="17" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="70" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C17" s="70"/>
       <c r="D17" s="70"/>
@@ -39219,7 +39218,7 @@
     </row>
     <row r="18" spans="2:16" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="287" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C18" s="288"/>
       <c r="D18" s="288"/>
@@ -39267,7 +39266,7 @@
     <row r="1" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="308" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C2" s="308"/>
       <c r="D2" s="308"/>
@@ -39275,32 +39274,32 @@
     <row r="3" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="180" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="181" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="181" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="181" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="181" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="181" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -39308,73 +39307,73 @@
     </row>
     <row r="11" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="180" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="181" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="181" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="181" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="181" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="181" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="181" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="181" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="180" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="181" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="181" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="181" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="181" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="181" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -39456,7 +39455,7 @@
     </row>
     <row r="5" spans="2:24" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="262" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C5" s="262"/>
       <c r="D5" s="262"/>
@@ -39465,7 +39464,7 @@
         <v>583896.55000000005</v>
       </c>
       <c r="F5" s="310" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G5" s="310"/>
       <c r="H5" s="310"/>
@@ -39498,49 +39497,49 @@
     </row>
     <row r="7" spans="2:24" s="266" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="250" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="250" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="250" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" s="250" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="250" t="s">
+      <c r="F7" s="251" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="250" t="s">
+      <c r="G7" s="251" t="s">
         <v>214</v>
       </c>
-      <c r="E7" s="250" t="s">
+      <c r="H7" s="250" t="s">
         <v>215</v>
       </c>
-      <c r="F7" s="251" t="s">
+      <c r="I7" s="250" t="s">
         <v>216</v>
       </c>
-      <c r="G7" s="251" t="s">
+      <c r="J7" s="250" t="s">
         <v>217</v>
       </c>
-      <c r="H7" s="250" t="s">
+      <c r="K7" s="250" t="s">
         <v>218</v>
       </c>
-      <c r="I7" s="250" t="s">
+      <c r="L7" s="250" t="s">
         <v>219</v>
       </c>
-      <c r="J7" s="250" t="s">
+      <c r="M7" s="251" t="s">
         <v>220</v>
       </c>
-      <c r="K7" s="250" t="s">
+      <c r="N7" s="251" t="s">
         <v>221</v>
       </c>
-      <c r="L7" s="250" t="s">
+      <c r="O7" s="251" t="s">
         <v>222</v>
       </c>
-      <c r="M7" s="251" t="s">
+      <c r="P7" s="251" t="s">
         <v>223</v>
-      </c>
-      <c r="N7" s="251" t="s">
-        <v>224</v>
-      </c>
-      <c r="O7" s="251" t="s">
-        <v>225</v>
-      </c>
-      <c r="P7" s="251" t="s">
-        <v>226</v>
       </c>
       <c r="Q7" s="261"/>
       <c r="R7" s="254"/>
@@ -40576,7 +40575,7 @@
     </row>
     <row r="41" spans="2:24" s="268" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="309" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C41" s="309"/>
       <c r="D41" s="309"/>
@@ -40731,7 +40730,7 @@
     <row r="48" spans="2:24" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" spans="2:19" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -40838,7 +40837,7 @@
     <row r="3" spans="2:40" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:40" s="91" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="151" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C4" s="152">
         <v>44197</v>
@@ -41407,7 +41406,7 @@
     <row r="18" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:28" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="70" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C19" s="70"/>
       <c r="D19" s="70"/>
@@ -41483,6 +41482,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -41491,7 +41496,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005104B4C06FD53E4DA82687A05841D03F" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="baecee92fc6a23d7c0a643ff746a4af3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7dc5af80-ab8f-4cff-b7cb-3463b3238b39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec4a10ea1a6ac0e8b531773a0b4fa9ce" ns2:_="">
     <xsd:import namespace="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
@@ -41665,13 +41670,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826E8F03-94FF-4994-AD38-2615BDB97036}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E2031B-F3FA-42B6-8826-6D4F98BAE269}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -41679,7 +41694,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E82769-0714-4D10-A15E-4D1316028E66}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41697,22 +41712,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826E8F03-94FF-4994-AD38-2615BDB97036}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{040b5de6-6e2e-46f2-bca1-507eb809bbf7}" enabled="1" method="Privileged" siteId="{56d7daaa-b378-45b3-aa11-af9402b401b9}" contentBits="0" removed="0"/>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.37-e08-review\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.37-rpa-validacion\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14336D1F-DDF0-4055-93D6-7193CA0DE83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BED47E-A6D9-45D6-A7AB-8267EF879B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Infor" sheetId="1" r:id="rId1"/>
@@ -1139,7 +1139,7 @@
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>Generado por RPA: 2026-05-11 10:45:50 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | ADVERTENCIA: PPO contiene anualidades de horas fuera del periodo CORE planificado.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 00:22:20 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
   </si>
 </sst>
 </file>
@@ -7490,7 +7490,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="59">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="D5" s="67"/>
       <c r="E5" s="65"/>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.37-rpa-validacion\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\Documents\UiPath\oportunidad-generar-core-v3\oportunidad-generar-core-main\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BED47E-A6D9-45D6-A7AB-8267EF879B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A9A057-EFBC-4357-B802-C531C7CE11B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1139,7 +1139,7 @@
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 00:22:20 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 01:01:48 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
   </si>
 </sst>
 </file>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\Documents\UiPath\oportunidad-generar-core-v3\oportunidad-generar-core-main\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.38-ep1\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A9A057-EFBC-4357-B802-C531C7CE11B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6A58DA-3C37-44AC-88A4-B8C191D40326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1139,7 +1139,7 @@
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 01:01:48 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:11:12 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
   </si>
 </sst>
 </file>
@@ -2959,6 +2959,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2968,16 +2975,9 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="D4" s="299"/>
       <c r="E4" s="27"/>
-      <c r="F4" s="316" t="s">
+      <c r="F4" s="312" t="s">
         <v>229</v>
       </c>
       <c r="G4" s="317"/>
@@ -8857,26 +8857,26 @@
       <c r="J4" s="242" t="s">
         <v>232</v>
       </c>
-      <c r="K4" s="316" t="s">
+      <c r="K4" s="312" t="s">
         <v>233</v>
       </c>
-      <c r="L4" s="316"/>
-      <c r="M4" s="316"/>
-      <c r="N4" s="316"/>
+      <c r="L4" s="312"/>
+      <c r="M4" s="312"/>
+      <c r="N4" s="312"/>
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="82" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="314" t="s">
+      <c r="C5" s="311" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="314"/>
+      <c r="D5" s="311"/>
       <c r="E5" s="27"/>
-      <c r="F5" s="314" t="s">
+      <c r="F5" s="311" t="s">
         <v>236</v>
       </c>
-      <c r="G5" s="314"/>
+      <c r="G5" s="311"/>
       <c r="H5" s="244">
         <v>0.5</v>
       </c>
@@ -8886,24 +8886,24 @@
       <c r="J5" s="234" t="s">
         <v>235</v>
       </c>
-      <c r="K5" s="314"/>
-      <c r="L5" s="314"/>
-      <c r="M5" s="314"/>
-      <c r="N5" s="314"/>
+      <c r="K5" s="311"/>
+      <c r="L5" s="311"/>
+      <c r="M5" s="311"/>
+      <c r="N5" s="311"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="82" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="314" t="s">
+      <c r="C6" s="311" t="s">
         <v>238</v>
       </c>
-      <c r="D6" s="314"/>
+      <c r="D6" s="311"/>
       <c r="E6" s="27"/>
-      <c r="F6" s="314" t="s">
+      <c r="F6" s="311" t="s">
         <v>239</v>
       </c>
-      <c r="G6" s="314"/>
+      <c r="G6" s="311"/>
       <c r="H6" s="244">
         <v>0.1</v>
       </c>
@@ -8911,26 +8911,26 @@
         <v>1000</v>
       </c>
       <c r="J6" s="234"/>
-      <c r="K6" s="314"/>
-      <c r="L6" s="314"/>
-      <c r="M6" s="314"/>
-      <c r="N6" s="314"/>
+      <c r="K6" s="311"/>
+      <c r="L6" s="311"/>
+      <c r="M6" s="311"/>
+      <c r="N6" s="311"/>
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="315">
+      <c r="C7" s="316">
         <v>10000</v>
       </c>
-      <c r="D7" s="315"/>
+      <c r="D7" s="316"/>
       <c r="E7" s="243" t="s">
         <v>241</v>
       </c>
-      <c r="F7" s="314" t="s">
+      <c r="F7" s="311" t="s">
         <v>242</v>
       </c>
-      <c r="G7" s="314"/>
+      <c r="G7" s="311"/>
       <c r="H7" s="244">
         <v>0.2</v>
       </c>
@@ -8938,18 +8938,18 @@
         <v>2000</v>
       </c>
       <c r="J7" s="234"/>
-      <c r="K7" s="314"/>
-      <c r="L7" s="314"/>
-      <c r="M7" s="314"/>
-      <c r="N7" s="314"/>
+      <c r="K7" s="311"/>
+      <c r="L7" s="311"/>
+      <c r="M7" s="311"/>
+      <c r="N7" s="311"/>
     </row>
     <row r="8" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
-      <c r="F8" s="314" t="s">
+      <c r="F8" s="311" t="s">
         <v>243</v>
       </c>
-      <c r="G8" s="314"/>
+      <c r="G8" s="311"/>
       <c r="H8" s="244">
         <v>0.1</v>
       </c>
@@ -8957,18 +8957,18 @@
         <v>1000</v>
       </c>
       <c r="J8" s="234"/>
-      <c r="K8" s="314"/>
-      <c r="L8" s="314"/>
-      <c r="M8" s="314"/>
-      <c r="N8" s="314"/>
+      <c r="K8" s="311"/>
+      <c r="L8" s="311"/>
+      <c r="M8" s="311"/>
+      <c r="N8" s="311"/>
     </row>
     <row r="9" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="27"/>
       <c r="E9" s="61"/>
-      <c r="F9" s="314" t="s">
+      <c r="F9" s="311" t="s">
         <v>244</v>
       </c>
-      <c r="G9" s="314"/>
+      <c r="G9" s="311"/>
       <c r="H9" s="244">
         <v>0.1</v>
       </c>
@@ -8976,10 +8976,10 @@
         <v>1000</v>
       </c>
       <c r="J9" s="234"/>
-      <c r="K9" s="314"/>
-      <c r="L9" s="314"/>
-      <c r="M9" s="314"/>
-      <c r="N9" s="314"/>
+      <c r="K9" s="311"/>
+      <c r="L9" s="311"/>
+      <c r="M9" s="311"/>
+      <c r="N9" s="311"/>
       <c r="O9" s="29"/>
       <c r="P9" s="29"/>
     </row>
@@ -10065,12 +10065,12 @@
       <c r="W45" s="26"/>
     </row>
     <row r="46" spans="2:23" s="94" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="311" t="s">
+      <c r="B46" s="313" t="s">
         <v>224</v>
       </c>
-      <c r="C46" s="311"/>
-      <c r="D46" s="311"/>
-      <c r="E46" s="311"/>
+      <c r="C46" s="313"/>
+      <c r="D46" s="313"/>
+      <c r="E46" s="313"/>
       <c r="F46" s="225">
         <f>SUM(F13:F45)</f>
         <v>3000</v>
@@ -10234,16 +10234,16 @@
       <c r="R55" s="29"/>
     </row>
     <row r="56" spans="2:22" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="312" t="s">
+      <c r="B56" s="314" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="313"/>
-      <c r="D56" s="313"/>
-      <c r="E56" s="313"/>
-      <c r="F56" s="313"/>
-      <c r="G56" s="313"/>
-      <c r="H56" s="313"/>
-      <c r="I56" s="313"/>
+      <c r="C56" s="315"/>
+      <c r="D56" s="315"/>
+      <c r="E56" s="315"/>
+      <c r="F56" s="315"/>
+      <c r="G56" s="315"/>
+      <c r="H56" s="315"/>
+      <c r="I56" s="315"/>
       <c r="J56" s="179"/>
       <c r="K56" s="179"/>
       <c r="L56" s="179"/>
@@ -10257,16 +10257,6 @@
   </sheetData>
   <autoFilter ref="B12:E12" xr:uid="{F0215733-3491-41E7-AEDA-44D9E214180D}"/>
   <mergeCells count="19">
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="K8:N8"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="C4:D4"/>
@@ -10276,6 +10266,16 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C10">
@@ -41482,18 +41482,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41671,6 +41671,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E2031B-F3FA-42B6-8826-6D4F98BAE269}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826E8F03-94FF-4994-AD38-2615BDB97036}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -41682,14 +41690,6 @@
     <ds:schemaRef ds:uri="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E2031B-F3FA-42B6-8826-6D4F98BAE269}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.38-ep1\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.39-ep2\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6A58DA-3C37-44AC-88A4-B8C191D40326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B121C3B-8777-417D-B8C1-6870FCBB4C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1139,7 +1139,7 @@
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:11:12 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:27:34 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
   </si>
 </sst>
 </file>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.39-ep2\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.40-ep3\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B121C3B-8777-417D-B8C1-6870FCBB4C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24988C2-A48F-49E4-AD8B-46CFB1404405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1139,7 +1139,7 @@
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:27:34 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 02:48:25 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
   </si>
 </sst>
 </file>
@@ -2959,13 +2959,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2975,9 +2968,16 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="D4" s="299"/>
       <c r="E4" s="27"/>
-      <c r="F4" s="312" t="s">
+      <c r="F4" s="316" t="s">
         <v>229</v>
       </c>
       <c r="G4" s="317"/>
@@ -8857,26 +8857,26 @@
       <c r="J4" s="242" t="s">
         <v>232</v>
       </c>
-      <c r="K4" s="312" t="s">
+      <c r="K4" s="316" t="s">
         <v>233</v>
       </c>
-      <c r="L4" s="312"/>
-      <c r="M4" s="312"/>
-      <c r="N4" s="312"/>
+      <c r="L4" s="316"/>
+      <c r="M4" s="316"/>
+      <c r="N4" s="316"/>
     </row>
     <row r="5" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="82" t="s">
         <v>234</v>
       </c>
-      <c r="C5" s="311" t="s">
+      <c r="C5" s="314" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="311"/>
+      <c r="D5" s="314"/>
       <c r="E5" s="27"/>
-      <c r="F5" s="311" t="s">
+      <c r="F5" s="314" t="s">
         <v>236</v>
       </c>
-      <c r="G5" s="311"/>
+      <c r="G5" s="314"/>
       <c r="H5" s="244">
         <v>0.5</v>
       </c>
@@ -8886,24 +8886,24 @@
       <c r="J5" s="234" t="s">
         <v>235</v>
       </c>
-      <c r="K5" s="311"/>
-      <c r="L5" s="311"/>
-      <c r="M5" s="311"/>
-      <c r="N5" s="311"/>
+      <c r="K5" s="314"/>
+      <c r="L5" s="314"/>
+      <c r="M5" s="314"/>
+      <c r="N5" s="314"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="82" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="311" t="s">
+      <c r="C6" s="314" t="s">
         <v>238</v>
       </c>
-      <c r="D6" s="311"/>
+      <c r="D6" s="314"/>
       <c r="E6" s="27"/>
-      <c r="F6" s="311" t="s">
+      <c r="F6" s="314" t="s">
         <v>239</v>
       </c>
-      <c r="G6" s="311"/>
+      <c r="G6" s="314"/>
       <c r="H6" s="244">
         <v>0.1</v>
       </c>
@@ -8911,26 +8911,26 @@
         <v>1000</v>
       </c>
       <c r="J6" s="234"/>
-      <c r="K6" s="311"/>
-      <c r="L6" s="311"/>
-      <c r="M6" s="311"/>
-      <c r="N6" s="311"/>
+      <c r="K6" s="314"/>
+      <c r="L6" s="314"/>
+      <c r="M6" s="314"/>
+      <c r="N6" s="314"/>
     </row>
     <row r="7" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="316">
+      <c r="C7" s="315">
         <v>10000</v>
       </c>
-      <c r="D7" s="316"/>
+      <c r="D7" s="315"/>
       <c r="E7" s="243" t="s">
         <v>241</v>
       </c>
-      <c r="F7" s="311" t="s">
+      <c r="F7" s="314" t="s">
         <v>242</v>
       </c>
-      <c r="G7" s="311"/>
+      <c r="G7" s="314"/>
       <c r="H7" s="244">
         <v>0.2</v>
       </c>
@@ -8938,18 +8938,18 @@
         <v>2000</v>
       </c>
       <c r="J7" s="234"/>
-      <c r="K7" s="311"/>
-      <c r="L7" s="311"/>
-      <c r="M7" s="311"/>
-      <c r="N7" s="311"/>
+      <c r="K7" s="314"/>
+      <c r="L7" s="314"/>
+      <c r="M7" s="314"/>
+      <c r="N7" s="314"/>
     </row>
     <row r="8" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
-      <c r="F8" s="311" t="s">
+      <c r="F8" s="314" t="s">
         <v>243</v>
       </c>
-      <c r="G8" s="311"/>
+      <c r="G8" s="314"/>
       <c r="H8" s="244">
         <v>0.1</v>
       </c>
@@ -8957,18 +8957,18 @@
         <v>1000</v>
       </c>
       <c r="J8" s="234"/>
-      <c r="K8" s="311"/>
-      <c r="L8" s="311"/>
-      <c r="M8" s="311"/>
-      <c r="N8" s="311"/>
+      <c r="K8" s="314"/>
+      <c r="L8" s="314"/>
+      <c r="M8" s="314"/>
+      <c r="N8" s="314"/>
     </row>
     <row r="9" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D9" s="27"/>
       <c r="E9" s="61"/>
-      <c r="F9" s="311" t="s">
+      <c r="F9" s="314" t="s">
         <v>244</v>
       </c>
-      <c r="G9" s="311"/>
+      <c r="G9" s="314"/>
       <c r="H9" s="244">
         <v>0.1</v>
       </c>
@@ -8976,10 +8976,10 @@
         <v>1000</v>
       </c>
       <c r="J9" s="234"/>
-      <c r="K9" s="311"/>
-      <c r="L9" s="311"/>
-      <c r="M9" s="311"/>
-      <c r="N9" s="311"/>
+      <c r="K9" s="314"/>
+      <c r="L9" s="314"/>
+      <c r="M9" s="314"/>
+      <c r="N9" s="314"/>
       <c r="O9" s="29"/>
       <c r="P9" s="29"/>
     </row>
@@ -10065,12 +10065,12 @@
       <c r="W45" s="26"/>
     </row>
     <row r="46" spans="2:23" s="94" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="313" t="s">
+      <c r="B46" s="311" t="s">
         <v>224</v>
       </c>
-      <c r="C46" s="313"/>
-      <c r="D46" s="313"/>
-      <c r="E46" s="313"/>
+      <c r="C46" s="311"/>
+      <c r="D46" s="311"/>
+      <c r="E46" s="311"/>
       <c r="F46" s="225">
         <f>SUM(F13:F45)</f>
         <v>3000</v>
@@ -10234,16 +10234,16 @@
       <c r="R55" s="29"/>
     </row>
     <row r="56" spans="2:22" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="314" t="s">
+      <c r="B56" s="312" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="315"/>
-      <c r="D56" s="315"/>
-      <c r="E56" s="315"/>
-      <c r="F56" s="315"/>
-      <c r="G56" s="315"/>
-      <c r="H56" s="315"/>
-      <c r="I56" s="315"/>
+      <c r="C56" s="313"/>
+      <c r="D56" s="313"/>
+      <c r="E56" s="313"/>
+      <c r="F56" s="313"/>
+      <c r="G56" s="313"/>
+      <c r="H56" s="313"/>
+      <c r="I56" s="313"/>
       <c r="J56" s="179"/>
       <c r="K56" s="179"/>
       <c r="L56" s="179"/>
@@ -10257,6 +10257,16 @@
   </sheetData>
   <autoFilter ref="B12:E12" xr:uid="{F0215733-3491-41E7-AEDA-44D9E214180D}"/>
   <mergeCells count="19">
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K8:N8"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="C4:D4"/>
@@ -10266,16 +10276,6 @@
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C10">
@@ -41482,21 +41482,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005104B4C06FD53E4DA82687A05841D03F" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="baecee92fc6a23d7c0a643ff746a4af3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7dc5af80-ab8f-4cff-b7cb-3463b3238b39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec4a10ea1a6ac0e8b531773a0b4fa9ce" ns2:_="">
     <xsd:import namespace="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
@@ -41670,10 +41655,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E2031B-F3FA-42B6-8826-6D4F98BAE269}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E82769-0714-4D10-A15E-4D1316028E66}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -41695,19 +41705,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E82769-0714-4D10-A15E-4D1316028E66}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E2031B-F3FA-42B6-8826-6D4F98BAE269}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7dc5af80-ab8f-4cff-b7cb-3463b3238b39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.42-ep4\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.55-ep5\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0443017F-29E5-496A-8A52-DA1CC1C91B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB6B18C-277D-42CE-9F91-6B4403C5AE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1142,7 +1142,7 @@
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 03:08:04 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 04:27:10 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
   </si>
 </sst>
 </file>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.55-ep5\content\data\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.56-ep6\content\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB6B18C-277D-42CE-9F91-6B4403C5AE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BD7FAD-7265-404F-9557-08BCB70EB594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="740" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1142,7 +1142,7 @@
     <t>ARIBA-TEST-001</t>
   </si>
   <si>
-    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 04:27:10 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
+    <t>RPA_VALIDACION: Generado por RPA: 2026-05-12 04:39:15 | PPO=20250256445  PPO_NuevaTerminalPVR v2 1.xlsm | NumeroSF=20250256445 | Tipo=PC | Campos PPO=7 | Trazabilidad: PPO=baseline; SAP/SF=datos de prueba hardcodeados en Main.xaml; reglas=recursos/gastos/compras prorrateados por anualidad, riesgos/garantia al ultimo mes, facturacion y realizado vacios; pendiente JP=revisar intercompany, externos y planificacion mensual. | PC: detectadas anualidades fuera de calendario CORE. Calendario 2025-11 a 2026-10. Baseline recursos PPO: 367.515,14 EUR. Recursos planificados: 324.095,05 EUR. Pendiente fuera de calendario: 1.720 h / 43.420,09 EUR. Años afectados: 2027, 2028. Revisión requerida por JP.</t>
   </si>
 </sst>
 </file>
